--- a/SPC26S1 - 05 May.xlsx
+++ b/SPC26S1 - 05 May.xlsx
@@ -2811,7 +2811,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="95">
+  <dxfs count="103">
     <dxf>
       <font>
         <color rgb="FF1F4E79"/>
@@ -3781,6 +3781,62 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC6E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFBDD7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD9D2E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9F9F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE4A0C8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -7486,6 +7542,32 @@
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A2:AN1000">
+    <cfRule type="expression" dxfId="95" priority="16">
+      <formula>TRIM($A2)="PAID"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="96" priority="17">
+      <formula>TRIM($A2)="Finalized"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="97" priority="18">
+      <formula>TRIM($A2)="Received"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="98" priority="19">
+      <formula>TRIM($A2)="Pending"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="99" priority="20">
+      <formula>TRIM($A2)="Under Review"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="100" priority="21">
+      <formula>TRIM($A2)="Denied"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="22">
+      <formula>TRIM($A2)="Rejected"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="23">
+      <formula>TRIM($A2)="Not found"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A31" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
@@ -11597,6 +11679,32 @@
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A2:AN1000">
+    <cfRule type="expression" dxfId="95" priority="21">
+      <formula>TRIM($A2)="PAID"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="96" priority="22">
+      <formula>TRIM($A2)="Finalized"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="97" priority="23">
+      <formula>TRIM($A2)="Received"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="98" priority="24">
+      <formula>TRIM($A2)="Pending"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="99" priority="25">
+      <formula>TRIM($A2)="Under Review"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="100" priority="26">
+      <formula>TRIM($A2)="Denied"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="27">
+      <formula>TRIM($A2)="Rejected"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="28">
+      <formula>TRIM($A2)="Not found"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A35" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
@@ -12539,6 +12647,32 @@
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A2:AN1000">
+    <cfRule type="expression" dxfId="95" priority="21">
+      <formula>TRIM($A2)="PAID"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="96" priority="22">
+      <formula>TRIM($A2)="Finalized"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="97" priority="23">
+      <formula>TRIM($A2)="Received"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="98" priority="24">
+      <formula>TRIM($A2)="Pending"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="99" priority="25">
+      <formula>TRIM($A2)="Under Review"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="100" priority="26">
+      <formula>TRIM($A2)="Denied"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="27">
+      <formula>TRIM($A2)="Rejected"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="28">
+      <formula>TRIM($A2)="Not found"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A7" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
@@ -15261,6 +15395,32 @@
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A2:AN1000">
+    <cfRule type="expression" dxfId="95" priority="21">
+      <formula>TRIM($A2)="PAID"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="96" priority="22">
+      <formula>TRIM($A2)="Finalized"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="97" priority="23">
+      <formula>TRIM($A2)="Received"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="98" priority="24">
+      <formula>TRIM($A2)="Pending"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="99" priority="25">
+      <formula>TRIM($A2)="Under Review"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="100" priority="26">
+      <formula>TRIM($A2)="Denied"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="27">
+      <formula>TRIM($A2)="Rejected"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="28">
+      <formula>TRIM($A2)="Not found"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A23" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
@@ -17202,6 +17362,32 @@
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A2:AN1000">
+    <cfRule type="expression" dxfId="95" priority="21">
+      <formula>TRIM($A2)="PAID"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="96" priority="22">
+      <formula>TRIM($A2)="Finalized"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="97" priority="23">
+      <formula>TRIM($A2)="Received"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="98" priority="24">
+      <formula>TRIM($A2)="Pending"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="99" priority="25">
+      <formula>TRIM($A2)="Under Review"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="100" priority="26">
+      <formula>TRIM($A2)="Denied"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="27">
+      <formula>TRIM($A2)="Rejected"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="28">
+      <formula>TRIM($A2)="Not found"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A16" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
@@ -17217,7 +17403,7 @@
   <sheetPr>
     <tabColor rgb="FF1F4E79"/>
   </sheetPr>
-  <dimension ref="A1:A37"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="118" customWidth="1"/>
@@ -17392,7 +17578,127 @@
         <v>522</v>
       </c>
     </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="9"/>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Row colours by Claim Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="45" customHeight="1">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Each claim row is shaded by its Claim Status (column A) using conditional formatting, so the colour follows the status automatically when it is changed. Rows with no Claim Status keep their normal formatting. The deadline countdown columns keep their own colour bands.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PAID - green</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Finalized - blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Received - lavender</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Pending - yellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Under Review - orange</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Denied - red</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Rejected - pink</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Not found - grey</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Any other status is left unshaded.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="A41">
+    <cfRule type="expression" dxfId="95" priority="1">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A42">
+    <cfRule type="expression" dxfId="96" priority="2">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A43">
+    <cfRule type="expression" dxfId="97" priority="3">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A44">
+    <cfRule type="expression" dxfId="98" priority="4">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A45">
+    <cfRule type="expression" dxfId="99" priority="5">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A46">
+    <cfRule type="expression" dxfId="100" priority="6">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A47">
+    <cfRule type="expression" dxfId="101" priority="7">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A48">
+    <cfRule type="expression" dxfId="102" priority="8">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/SPC26S1 - 05 May.xlsx
+++ b/SPC26S1 - 05 May.xlsx
@@ -2633,7 +2633,7 @@
     <t>107 claims with a date of service in 2026-05 May, split into one sheet per specialty: BH, DME, GAE, ORTHO, US.</t>
   </si>
   <si>
-    <t>Every specialty sheet is sorted in three groups: claims with an empty Latest Date Worked (column K) at the top, then the other open claims, and Finalized and PAID claims at the bottom (a Finalized or PAID claim goes to the bottom even when its Latest Date Worked is empty). Within each group, rows are ordered by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: five days or less left is shaded red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
+    <t>Every specialty sheet is sorted in three groups: claims with an empty Latest Date Worked (column K) at the top, then the other open claims, and Finalized and PAID claims at the bottom (a Finalized or PAID claim with an empty Latest Date Worked stays in the top group). Within each group, rows are ordered by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: five days or less left is shaded red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
   </si>
   <si>
     <t>Deadline order within each group, with the colour band each row gets, counted on 19 September 2026:</t>
@@ -7857,54 +7857,56 @@
     </row>
     <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>530</v>
+        <v>116</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="C3" s="3"/>
+        <v>252</v>
+      </c>
+      <c r="C3" s="3">
+        <v>46249</v>
+      </c>
       <c r="D3" s="4">
-        <v>559374682</v>
+        <v>559009959</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>313</v>
+        <v>253</v>
       </c>
       <c r="F3" s="6">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>95</v>
+        <v>246</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>95</v>
+        <v>246</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>223</v>
+        <v>198</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="12">
         <f ca="1">IF($O3="","",$O3-TODAY())</f>
-        <v>-70</v>
-      </c>
-      <c r="M3" s="12" t="str">
+        <v>209</v>
+      </c>
+      <c r="M3" s="12">
         <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
-        <v/>
-      </c>
-      <c r="N3" s="12" t="str">
-        <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
-        <v/>
+        <v>311</v>
+      </c>
+      <c r="N3" s="12">
+        <f ca="1">IF($C3="","",$C3+120-TODAY())</f>
+        <v>66</v>
       </c>
       <c r="O3" s="6">
-        <v>46233</v>
+        <v>46512</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="R3" s="5" t="s">
         <v>50</v>
@@ -7913,52 +7915,54 @@
         <v>49</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="U3" s="5" t="s">
         <v>49</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="W3" s="5"/>
       <c r="X3" s="5"/>
       <c r="Y3" s="5" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="Z3" s="7">
-        <v>36353.800000000003</v>
+        <v>2958.2</v>
       </c>
       <c r="AA3" s="7">
         <v>0</v>
       </c>
       <c r="AB3" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="6"/>
+        <v>88.28</v>
+      </c>
+      <c r="AC3" s="6">
+        <v>46197</v>
+      </c>
       <c r="AD3" s="7">
-        <v>36353.800000000003</v>
+        <v>2869.92</v>
       </c>
       <c r="AE3" s="4">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="AF3" s="5" t="s">
         <v>174</v>
       </c>
       <c r="AG3" s="5" t="s">
-        <v>225</v>
+        <v>254</v>
       </c>
       <c r="AH3" s="5"/>
       <c r="AI3" s="5"/>
       <c r="AJ3" s="4"/>
       <c r="AK3" s="5" t="s">
-        <v>178</v>
+        <v>255</v>
       </c>
       <c r="AL3" s="5" t="s">
-        <v>68</v>
+        <v>256</v>
       </c>
       <c r="AM3" s="6">
-        <v>46217</v>
+        <v>46155</v>
       </c>
       <c r="AN3" s="5" t="s">
         <v>179</v>
@@ -7966,56 +7970,56 @@
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>530</v>
+        <v>116</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="C4" s="3"/>
+        <v>257</v>
+      </c>
+      <c r="C4" s="3">
+        <v>46202</v>
+      </c>
       <c r="D4" s="4">
-        <v>559604554</v>
+        <v>559008757</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>169</v>
+        <v>258</v>
       </c>
       <c r="F4" s="6">
-        <v>46157</v>
+        <v>46150</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>95</v>
+        <v>259</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>95</v>
+        <v>246</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>170</v>
+        <v>259</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="K4" s="3">
-        <v>46244</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="K4" s="3"/>
       <c r="L4" s="12">
         <f ca="1">IF($O4="","",$O4-TODAY())</f>
-        <v>-56</v>
-      </c>
-      <c r="M4" s="12" t="str">
+        <v>212</v>
+      </c>
+      <c r="M4" s="12">
         <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
-        <v/>
-      </c>
-      <c r="N4" s="12" t="str">
-        <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
-        <v/>
+        <v>264</v>
+      </c>
+      <c r="N4" s="12">
+        <f ca="1">IF($C4="","",$C4+120-TODAY())</f>
+        <v>19</v>
       </c>
       <c r="O4" s="6">
-        <v>46247</v>
+        <v>46515</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="R4" s="5" t="s">
         <v>50</v>
@@ -8024,56 +8028,56 @@
         <v>49</v>
       </c>
       <c r="T4" s="5" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="U4" s="5" t="s">
         <v>49</v>
       </c>
       <c r="V4" s="5" t="s">
-        <v>172</v>
+        <v>248</v>
       </c>
       <c r="W4" s="5"/>
       <c r="X4" s="5"/>
       <c r="Y4" s="5" t="s">
-        <v>173</v>
+        <v>51</v>
       </c>
       <c r="Z4" s="7">
-        <v>36353.800000000003</v>
+        <v>6392.96</v>
       </c>
       <c r="AA4" s="7">
-        <v>0</v>
+        <v>5624.17</v>
       </c>
       <c r="AB4" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="6"/>
+        <v>612.53</v>
+      </c>
+      <c r="AC4" s="6">
+        <v>46202</v>
+      </c>
       <c r="AD4" s="7">
-        <v>36353.800000000003</v>
+        <v>156.26</v>
       </c>
       <c r="AE4" s="4">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="AF4" s="5" t="s">
-        <v>174</v>
+        <v>261</v>
       </c>
       <c r="AG4" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="AH4" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="AI4" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="AJ4" s="4"/>
+        <v>262</v>
+      </c>
+      <c r="AH4" s="5"/>
+      <c r="AI4" s="5"/>
+      <c r="AJ4" s="4">
+        <v>564922724</v>
+      </c>
       <c r="AK4" s="5" t="s">
-        <v>178</v>
+        <v>263</v>
       </c>
       <c r="AL4" s="5" t="s">
-        <v>68</v>
+        <v>264</v>
       </c>
       <c r="AM4" s="6">
-        <v>46217</v>
+        <v>46155</v>
       </c>
       <c r="AN4" s="5" t="s">
         <v>179</v>
@@ -8081,58 +8085,56 @@
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>180</v>
+        <v>292</v>
       </c>
       <c r="C5" s="3">
-        <v>46196</v>
+        <v>46209</v>
       </c>
       <c r="D5" s="4">
-        <v>559742691</v>
+        <v>561853521</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>181</v>
+        <v>293</v>
       </c>
       <c r="F5" s="6">
-        <v>46160</v>
+        <v>46168</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>95</v>
+        <v>246</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>95</v>
+        <v>246</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>44</v>
+        <v>294</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="K5" s="3">
-        <v>46245</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="K5" s="3"/>
       <c r="L5" s="12">
         <f ca="1">IF($O5="","",$O5-TODAY())</f>
-        <v>-53</v>
+        <v>230</v>
       </c>
       <c r="M5" s="12">
         <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="N5" s="12">
-        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
-        <v>258</v>
+        <f ca="1">IF($C5="","",$C5+120-TODAY())</f>
+        <v>26</v>
       </c>
       <c r="O5" s="6">
-        <v>46250</v>
+        <v>46533</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="R5" s="5" t="s">
         <v>50</v>
@@ -8141,52 +8143,54 @@
         <v>49</v>
       </c>
       <c r="T5" s="5" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="U5" s="5" t="s">
         <v>49</v>
       </c>
       <c r="V5" s="5" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="W5" s="5"/>
       <c r="X5" s="5"/>
       <c r="Y5" s="5" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="Z5" s="7">
-        <v>5916.4</v>
+        <v>18176.900000000001</v>
       </c>
       <c r="AA5" s="7">
         <v>0</v>
       </c>
       <c r="AB5" s="7">
-        <v>0</v>
+        <v>542.44000000000005</v>
       </c>
       <c r="AC5" s="6">
-        <v>46196</v>
+        <v>46209</v>
       </c>
       <c r="AD5" s="7">
-        <v>5916.4</v>
+        <v>17634.46</v>
       </c>
       <c r="AE5" s="4">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AF5" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="AG5" s="5"/>
+      <c r="AG5" s="5" t="s">
+        <v>296</v>
+      </c>
       <c r="AH5" s="5"/>
       <c r="AI5" s="5"/>
       <c r="AJ5" s="4"/>
       <c r="AK5" s="5" t="s">
-        <v>184</v>
+        <v>255</v>
       </c>
       <c r="AL5" s="5" t="s">
-        <v>185</v>
+        <v>256</v>
       </c>
       <c r="AM5" s="6">
-        <v>46162</v>
+        <v>46183</v>
       </c>
       <c r="AN5" s="5" t="s">
         <v>179</v>
@@ -8194,81 +8198,79 @@
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>186</v>
+        <v>292</v>
       </c>
       <c r="C6" s="3">
-        <v>46185</v>
+        <v>46249</v>
       </c>
       <c r="D6" s="4">
-        <v>561880042</v>
+        <v>561856360</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>187</v>
+        <v>297</v>
       </c>
       <c r="F6" s="6">
-        <v>46160</v>
+        <v>46168</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>188</v>
+        <v>246</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>188</v>
+        <v>246</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>44</v>
+        <v>272</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="K6" s="3">
-        <v>46245</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="K6" s="3"/>
       <c r="L6" s="12">
         <f ca="1">IF($O6="","",$O6-TODAY())</f>
-        <v>-53</v>
+        <v>230</v>
       </c>
       <c r="M6" s="12">
-        <f ca="1">IF($F6="","",$F6+90-TODAY())</f>
-        <v>-53</v>
+        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
+        <v>311</v>
       </c>
       <c r="N6" s="12">
-        <f ca="1">IF($C6="","",$C6+540-TODAY())</f>
-        <v>422</v>
+        <f ca="1">IF($C6="","",$C6+120-TODAY())</f>
+        <v>66</v>
       </c>
       <c r="O6" s="6">
-        <v>46250</v>
+        <v>46533</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>190</v>
+        <v>121</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>191</v>
+        <v>49</v>
       </c>
       <c r="T6" s="5" t="s">
-        <v>539</v>
+        <v>103</v>
       </c>
       <c r="U6" s="5" t="s">
         <v>49</v>
       </c>
       <c r="V6" s="5" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="W6" s="5"/>
       <c r="X6" s="5"/>
       <c r="Y6" s="5" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="Z6" s="7">
-        <v>72707.600000000006</v>
+        <v>2958.2</v>
       </c>
       <c r="AA6" s="7">
         <v>0</v>
@@ -8276,29 +8278,27 @@
       <c r="AB6" s="7">
         <v>0</v>
       </c>
-      <c r="AC6" s="6">
-        <v>46185</v>
-      </c>
+      <c r="AC6" s="6"/>
       <c r="AD6" s="7">
-        <v>72707.600000000006</v>
+        <v>2958.2</v>
       </c>
       <c r="AE6" s="4">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AF6" s="5" t="s">
         <v>174</v>
       </c>
       <c r="AG6" s="5" t="s">
-        <v>193</v>
+        <v>288</v>
       </c>
       <c r="AH6" s="5"/>
       <c r="AI6" s="5"/>
       <c r="AJ6" s="4"/>
       <c r="AK6" s="5" t="s">
-        <v>194</v>
+        <v>255</v>
       </c>
       <c r="AL6" s="5" t="s">
-        <v>86</v>
+        <v>256</v>
       </c>
       <c r="AM6" s="6">
         <v>46183</v>
@@ -8309,28 +8309,26 @@
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>219</v>
+        <v>530</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="C7" s="3">
-        <v>46184</v>
-      </c>
+        <v>534</v>
+      </c>
+      <c r="C7" s="3"/>
       <c r="D7" s="4">
-        <v>559750877</v>
+        <v>559374682</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>221</v>
+        <v>313</v>
       </c>
       <c r="F7" s="6">
-        <v>46161</v>
+        <v>46143</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>222</v>
+        <v>95</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>222</v>
+        <v>95</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>44</v>
@@ -8338,29 +8336,27 @@
       <c r="J7" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="K7" s="3">
-        <v>46252</v>
-      </c>
+      <c r="K7" s="3"/>
       <c r="L7" s="12">
         <f ca="1">IF($O7="","",$O7-TODAY())</f>
-        <v>-22</v>
-      </c>
-      <c r="M7" s="12">
+        <v>-70</v>
+      </c>
+      <c r="M7" s="12" t="str">
         <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
-        <v>246</v>
-      </c>
-      <c r="N7" s="12">
-        <f ca="1">IF($C7="","",$C7+90-TODAY())</f>
-        <v>-29</v>
+        <v/>
+      </c>
+      <c r="N7" s="12" t="str">
+        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
+        <v/>
       </c>
       <c r="O7" s="6">
-        <v>46281</v>
+        <v>46233</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>224</v>
+        <v>96</v>
       </c>
       <c r="R7" s="5" t="s">
         <v>50</v>
@@ -8369,7 +8365,7 @@
         <v>49</v>
       </c>
       <c r="T7" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="U7" s="5" t="s">
         <v>49</v>
@@ -8391,14 +8387,12 @@
       <c r="AB7" s="7">
         <v>0</v>
       </c>
-      <c r="AC7" s="6">
-        <v>46184</v>
-      </c>
+      <c r="AC7" s="6"/>
       <c r="AD7" s="7">
         <v>36353.800000000003</v>
       </c>
       <c r="AE7" s="4">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="AF7" s="5" t="s">
         <v>174</v>
@@ -8410,13 +8404,13 @@
       <c r="AI7" s="5"/>
       <c r="AJ7" s="4"/>
       <c r="AK7" s="5" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="AL7" s="5" t="s">
-        <v>226</v>
+        <v>68</v>
       </c>
       <c r="AM7" s="6">
-        <v>46162</v>
+        <v>46217</v>
       </c>
       <c r="AN7" s="5" t="s">
         <v>179</v>
@@ -8424,73 +8418,71 @@
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>87</v>
+        <v>530</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="C8" s="3">
-        <v>46190</v>
-      </c>
+        <v>550</v>
+      </c>
+      <c r="C8" s="3"/>
       <c r="D8" s="4">
-        <v>561859042</v>
+        <v>559604554</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>228</v>
+        <v>169</v>
       </c>
       <c r="F8" s="6">
-        <v>46168</v>
+        <v>46157</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>44</v>
+        <v>170</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>223</v>
+        <v>171</v>
       </c>
       <c r="K8" s="3">
-        <v>46253</v>
+        <v>46244</v>
       </c>
       <c r="L8" s="12">
         <f ca="1">IF($O8="","",$O8-TODAY())</f>
-        <v>-15</v>
-      </c>
-      <c r="M8" s="12">
-        <f ca="1">IF($F8="","",$F8+365-TODAY())</f>
-        <v>230</v>
-      </c>
-      <c r="N8" s="12">
-        <f ca="1">IF($F8="","",$F8+365-TODAY())</f>
-        <v>230</v>
+        <v>-56</v>
+      </c>
+      <c r="M8" s="12" t="str">
+        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
+        <v/>
+      </c>
+      <c r="N8" s="12" t="str">
+        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
+        <v/>
       </c>
       <c r="O8" s="6">
-        <v>46288</v>
+        <v>46247</v>
       </c>
       <c r="P8" s="5" t="s">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>229</v>
+        <v>96</v>
       </c>
       <c r="R8" s="5" t="s">
         <v>50</v>
       </c>
       <c r="S8" s="5" t="s">
-        <v>191</v>
+        <v>49</v>
       </c>
       <c r="T8" s="5" t="s">
         <v>50</v>
       </c>
       <c r="U8" s="5" t="s">
-        <v>191</v>
+        <v>49</v>
       </c>
       <c r="V8" s="5" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="W8" s="5"/>
       <c r="X8" s="5"/>
@@ -8506,36 +8498,34 @@
       <c r="AB8" s="7">
         <v>0</v>
       </c>
-      <c r="AC8" s="6">
-        <v>46190</v>
-      </c>
+      <c r="AC8" s="6"/>
       <c r="AD8" s="7">
         <v>36353.800000000003</v>
       </c>
       <c r="AE8" s="4">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="AF8" s="5" t="s">
         <v>174</v>
       </c>
       <c r="AG8" s="5" t="s">
-        <v>225</v>
+        <v>175</v>
       </c>
       <c r="AH8" s="5" t="s">
-        <v>211</v>
+        <v>176</v>
       </c>
       <c r="AI8" s="5" t="s">
-        <v>230</v>
+        <v>177</v>
       </c>
       <c r="AJ8" s="4"/>
       <c r="AK8" s="5" t="s">
-        <v>231</v>
+        <v>178</v>
       </c>
       <c r="AL8" s="5" t="s">
         <v>68</v>
       </c>
       <c r="AM8" s="6">
-        <v>46183</v>
+        <v>46217</v>
       </c>
       <c r="AN8" s="5" t="s">
         <v>179</v>
@@ -8546,67 +8536,67 @@
         <v>87</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="C9" s="3">
-        <v>46169</v>
+        <v>46196</v>
       </c>
       <c r="D9" s="4">
-        <v>559740566</v>
+        <v>559742691</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>233</v>
+        <v>181</v>
       </c>
       <c r="F9" s="6">
-        <v>46146</v>
+        <v>46160</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>234</v>
+        <v>95</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>234</v>
+        <v>95</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>223</v>
+        <v>182</v>
       </c>
       <c r="K9" s="3">
-        <v>46254</v>
+        <v>46245</v>
       </c>
       <c r="L9" s="12">
         <f ca="1">IF($O9="","",$O9-TODAY())</f>
-        <v>23</v>
+        <v>-53</v>
       </c>
       <c r="M9" s="12">
-        <f ca="1">IF($F9="","",$F9+365-TODAY())</f>
-        <v>208</v>
+        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
+        <v>258</v>
       </c>
       <c r="N9" s="12">
-        <f ca="1">IF($F9="","",$F9+365-TODAY())</f>
-        <v>208</v>
+        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
+        <v>258</v>
       </c>
       <c r="O9" s="6">
-        <v>46326</v>
+        <v>46250</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>235</v>
+        <v>96</v>
       </c>
       <c r="R9" s="5" t="s">
         <v>50</v>
       </c>
       <c r="S9" s="5" t="s">
-        <v>191</v>
+        <v>49</v>
       </c>
       <c r="T9" s="5" t="s">
         <v>50</v>
       </c>
       <c r="U9" s="5" t="s">
-        <v>191</v>
+        <v>49</v>
       </c>
       <c r="V9" s="5" t="s">
         <v>183</v>
@@ -8617,7 +8607,7 @@
         <v>173</v>
       </c>
       <c r="Z9" s="7">
-        <v>36353.800000000003</v>
+        <v>5916.4</v>
       </c>
       <c r="AA9" s="7">
         <v>0</v>
@@ -8626,20 +8616,18 @@
         <v>0</v>
       </c>
       <c r="AC9" s="6">
-        <v>46169</v>
+        <v>46196</v>
       </c>
       <c r="AD9" s="7">
-        <v>36353.800000000003</v>
+        <v>5916.4</v>
       </c>
       <c r="AE9" s="4">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="AF9" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="AG9" s="5" t="s">
-        <v>225</v>
-      </c>
+      <c r="AG9" s="5"/>
       <c r="AH9" s="5"/>
       <c r="AI9" s="5"/>
       <c r="AJ9" s="4"/>
@@ -8661,78 +8649,78 @@
         <v>87</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>239</v>
+        <v>186</v>
       </c>
       <c r="C10" s="3">
-        <v>46195</v>
+        <v>46185</v>
       </c>
       <c r="D10" s="4">
-        <v>561866854</v>
+        <v>561880042</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>240</v>
+        <v>187</v>
       </c>
       <c r="F10" s="6">
-        <v>46170</v>
+        <v>46160</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>234</v>
+        <v>188</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>234</v>
+        <v>188</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>241</v>
+        <v>189</v>
       </c>
       <c r="K10" s="3">
-        <v>46254</v>
+        <v>46245</v>
       </c>
       <c r="L10" s="12">
         <f ca="1">IF($O10="","",$O10-TODAY())</f>
-        <v>47</v>
+        <v>-53</v>
       </c>
       <c r="M10" s="12">
-        <f ca="1">IF($F10="","",$F10+365-TODAY())</f>
-        <v>232</v>
+        <f ca="1">IF($F10="","",$F10+90-TODAY())</f>
+        <v>-53</v>
       </c>
       <c r="N10" s="12">
-        <f ca="1">IF($F10="","",$F10+365-TODAY())</f>
-        <v>232</v>
+        <f ca="1">IF($C10="","",$C10+540-TODAY())</f>
+        <v>422</v>
       </c>
       <c r="O10" s="6">
-        <v>46350</v>
+        <v>46250</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>235</v>
+        <v>190</v>
       </c>
       <c r="R10" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="S10" s="5" t="s">
         <v>191</v>
       </c>
       <c r="T10" s="5" t="s">
-        <v>50</v>
+        <v>539</v>
       </c>
       <c r="U10" s="5" t="s">
-        <v>191</v>
+        <v>49</v>
       </c>
       <c r="V10" s="5" t="s">
-        <v>242</v>
+        <v>183</v>
       </c>
       <c r="W10" s="5"/>
       <c r="X10" s="5"/>
       <c r="Y10" s="5" t="s">
-        <v>51</v>
+        <v>192</v>
       </c>
       <c r="Z10" s="7">
-        <v>6392.96</v>
+        <v>72707.600000000006</v>
       </c>
       <c r="AA10" s="7">
         <v>0</v>
@@ -8741,30 +8729,28 @@
         <v>0</v>
       </c>
       <c r="AC10" s="6">
-        <v>46195</v>
+        <v>46185</v>
       </c>
       <c r="AD10" s="7">
-        <v>6392.96</v>
+        <v>72707.600000000006</v>
       </c>
       <c r="AE10" s="4">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="AF10" s="5" t="s">
-        <v>230</v>
+        <v>174</v>
       </c>
       <c r="AG10" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="AH10" s="5" t="s">
-        <v>206</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="AH10" s="5"/>
       <c r="AI10" s="5"/>
       <c r="AJ10" s="4"/>
       <c r="AK10" s="5" t="s">
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="AL10" s="5" t="s">
-        <v>243</v>
+        <v>86</v>
       </c>
       <c r="AM10" s="6">
         <v>46183</v>
@@ -8775,58 +8761,58 @@
     </row>
     <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>87</v>
+        <v>219</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="C11" s="3">
-        <v>46156</v>
+        <v>46184</v>
       </c>
       <c r="D11" s="4">
-        <v>559006292</v>
+        <v>559750877</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>245</v>
+        <v>221</v>
       </c>
       <c r="F11" s="6">
-        <v>46147</v>
+        <v>46161</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>247</v>
+        <v>223</v>
       </c>
       <c r="K11" s="3">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="L11" s="12">
         <f ca="1">IF($O11="","",$O11-TODAY())</f>
-        <v>209</v>
+        <v>-22</v>
       </c>
       <c r="M11" s="12">
         <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
-        <v>218</v>
+        <v>246</v>
       </c>
       <c r="N11" s="12">
-        <f ca="1">IF($C11="","",$C11+120-TODAY())</f>
-        <v>-27</v>
+        <f ca="1">IF($C11="","",$C11+90-TODAY())</f>
+        <v>-29</v>
       </c>
       <c r="O11" s="6">
-        <v>46512</v>
+        <v>46281</v>
       </c>
       <c r="P11" s="5" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>121</v>
+        <v>224</v>
       </c>
       <c r="R11" s="5" t="s">
         <v>50</v>
@@ -8835,21 +8821,21 @@
         <v>49</v>
       </c>
       <c r="T11" s="5" t="s">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="U11" s="5" t="s">
         <v>49</v>
       </c>
       <c r="V11" s="5" t="s">
-        <v>248</v>
+        <v>183</v>
       </c>
       <c r="W11" s="5"/>
       <c r="X11" s="5"/>
       <c r="Y11" s="5" t="s">
-        <v>51</v>
+        <v>173</v>
       </c>
       <c r="Z11" s="7">
-        <v>5320.49</v>
+        <v>36353.800000000003</v>
       </c>
       <c r="AA11" s="7">
         <v>0</v>
@@ -8858,29 +8844,31 @@
         <v>0</v>
       </c>
       <c r="AC11" s="6">
-        <v>46156</v>
+        <v>46184</v>
       </c>
       <c r="AD11" s="7">
-        <v>5320.49</v>
+        <v>36353.800000000003</v>
       </c>
       <c r="AE11" s="4">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="AF11" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="AG11" s="5"/>
+        <v>174</v>
+      </c>
+      <c r="AG11" s="5" t="s">
+        <v>225</v>
+      </c>
       <c r="AH11" s="5"/>
       <c r="AI11" s="5"/>
       <c r="AJ11" s="4"/>
       <c r="AK11" s="5" t="s">
-        <v>250</v>
+        <v>202</v>
       </c>
       <c r="AL11" s="5" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="AM11" s="6">
-        <v>46155</v>
+        <v>46162</v>
       </c>
       <c r="AN11" s="5" t="s">
         <v>179</v>
@@ -8891,67 +8879,67 @@
         <v>87</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>265</v>
+        <v>227</v>
       </c>
       <c r="C12" s="3">
-        <v>46185</v>
+        <v>46190</v>
       </c>
       <c r="D12" s="4">
-        <v>561877866</v>
+        <v>561859042</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>266</v>
+        <v>228</v>
       </c>
       <c r="F12" s="6">
-        <v>46150</v>
+        <v>46168</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>246</v>
+        <v>63</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>246</v>
+        <v>63</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>189</v>
+        <v>223</v>
       </c>
       <c r="K12" s="3">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="L12" s="12">
         <f ca="1">IF($O12="","",$O12-TODAY())</f>
-        <v>212</v>
+        <v>-15</v>
       </c>
       <c r="M12" s="12">
-        <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
-        <v>247</v>
+        <f ca="1">IF($F12="","",$F12+365-TODAY())</f>
+        <v>230</v>
       </c>
       <c r="N12" s="12">
-        <f ca="1">IF($C12="","",$C12+120-TODAY())</f>
-        <v>2</v>
+        <f ca="1">IF($F12="","",$F12+365-TODAY())</f>
+        <v>230</v>
       </c>
       <c r="O12" s="6">
-        <v>46515</v>
+        <v>46288</v>
       </c>
       <c r="P12" s="5" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="Q12" s="5" t="s">
-        <v>121</v>
+        <v>229</v>
       </c>
       <c r="R12" s="5" t="s">
         <v>50</v>
       </c>
       <c r="S12" s="5" t="s">
-        <v>49</v>
+        <v>191</v>
       </c>
       <c r="T12" s="5" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="U12" s="5" t="s">
-        <v>49</v>
+        <v>191</v>
       </c>
       <c r="V12" s="5" t="s">
         <v>183</v>
@@ -8959,10 +8947,10 @@
       <c r="W12" s="5"/>
       <c r="X12" s="5"/>
       <c r="Y12" s="5" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="Z12" s="7">
-        <v>72707.600000000006</v>
+        <v>36353.800000000003</v>
       </c>
       <c r="AA12" s="7">
         <v>0</v>
@@ -8971,13 +8959,13 @@
         <v>0</v>
       </c>
       <c r="AC12" s="6">
-        <v>46185</v>
+        <v>46190</v>
       </c>
       <c r="AD12" s="7">
-        <v>72707.600000000006</v>
+        <v>36353.800000000003</v>
       </c>
       <c r="AE12" s="4">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="AF12" s="5" t="s">
         <v>174</v>
@@ -8986,15 +8974,17 @@
         <v>225</v>
       </c>
       <c r="AH12" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="AI12" s="5"/>
+        <v>211</v>
+      </c>
+      <c r="AI12" s="5" t="s">
+        <v>230</v>
+      </c>
       <c r="AJ12" s="4"/>
       <c r="AK12" s="5" t="s">
-        <v>268</v>
+        <v>231</v>
       </c>
       <c r="AL12" s="5" t="s">
-        <v>269</v>
+        <v>68</v>
       </c>
       <c r="AM12" s="6">
         <v>46183</v>
@@ -9005,70 +8995,70 @@
     </row>
     <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>270</v>
+        <v>232</v>
       </c>
       <c r="C13" s="3">
-        <v>46211</v>
+        <v>46169</v>
       </c>
       <c r="D13" s="4">
-        <v>559783560</v>
+        <v>559740566</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>271</v>
+        <v>233</v>
       </c>
       <c r="F13" s="6">
-        <v>46156</v>
+        <v>46146</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>272</v>
+        <v>234</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>272</v>
+        <v>44</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>182</v>
+        <v>223</v>
       </c>
       <c r="K13" s="3">
         <v>46254</v>
       </c>
       <c r="L13" s="12">
         <f ca="1">IF($O13="","",$O13-TODAY())</f>
-        <v>218</v>
+        <v>23</v>
       </c>
       <c r="M13" s="12">
-        <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
-        <v>273</v>
+        <f ca="1">IF($F13="","",$F13+365-TODAY())</f>
+        <v>208</v>
       </c>
       <c r="N13" s="12">
-        <f ca="1">IF($C13="","",$C13+120-TODAY())</f>
-        <v>28</v>
+        <f ca="1">IF($F13="","",$F13+365-TODAY())</f>
+        <v>208</v>
       </c>
       <c r="O13" s="6">
-        <v>46521</v>
+        <v>46326</v>
       </c>
       <c r="P13" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>121</v>
+        <v>235</v>
       </c>
       <c r="R13" s="5" t="s">
         <v>50</v>
       </c>
       <c r="S13" s="5" t="s">
-        <v>49</v>
+        <v>191</v>
       </c>
       <c r="T13" s="5" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="U13" s="5" t="s">
-        <v>49</v>
+        <v>191</v>
       </c>
       <c r="V13" s="5" t="s">
         <v>183</v>
@@ -9079,39 +9069,37 @@
         <v>173</v>
       </c>
       <c r="Z13" s="7">
-        <v>5916.4</v>
+        <v>36353.800000000003</v>
       </c>
       <c r="AA13" s="7">
         <v>0</v>
       </c>
       <c r="AB13" s="7">
-        <v>176.56</v>
+        <v>0</v>
       </c>
       <c r="AC13" s="6">
-        <v>46211</v>
+        <v>46169</v>
       </c>
       <c r="AD13" s="7">
-        <v>5739.84</v>
+        <v>36353.800000000003</v>
       </c>
       <c r="AE13" s="4">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="AF13" s="5" t="s">
         <v>174</v>
       </c>
       <c r="AG13" s="5" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="AH13" s="5"/>
       <c r="AI13" s="5"/>
-      <c r="AJ13" s="4">
-        <v>562576876</v>
-      </c>
+      <c r="AJ13" s="4"/>
       <c r="AK13" s="5" t="s">
-        <v>263</v>
+        <v>184</v>
       </c>
       <c r="AL13" s="5" t="s">
-        <v>264</v>
+        <v>185</v>
       </c>
       <c r="AM13" s="6">
         <v>46162</v>
@@ -9125,80 +9113,78 @@
         <v>87</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>298</v>
+        <v>239</v>
       </c>
       <c r="C14" s="3">
-        <v>46204</v>
+        <v>46195</v>
       </c>
       <c r="D14" s="4">
-        <v>563514079</v>
+        <v>561866854</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>299</v>
+        <v>240</v>
       </c>
       <c r="F14" s="6">
         <v>46170</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>300</v>
+        <v>44</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>301</v>
+        <v>241</v>
       </c>
       <c r="K14" s="3">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="L14" s="12">
         <f ca="1">IF($O14="","",$O14-TODAY())</f>
+        <v>47</v>
+      </c>
+      <c r="M14" s="12">
+        <f ca="1">IF($F14="","",$F14+365-TODAY())</f>
         <v>232</v>
       </c>
-      <c r="M14" s="12">
-        <f ca="1">IF($C14="","",$C14+365-TODAY())</f>
-        <v>266</v>
-      </c>
       <c r="N14" s="12">
-        <f ca="1">IF($C14="","",$C14+120-TODAY())</f>
-        <v>21</v>
+        <f ca="1">IF($F14="","",$F14+365-TODAY())</f>
+        <v>232</v>
       </c>
       <c r="O14" s="6">
-        <v>46535</v>
+        <v>46350</v>
       </c>
       <c r="P14" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>121</v>
+        <v>235</v>
       </c>
       <c r="R14" s="5" t="s">
         <v>50</v>
       </c>
       <c r="S14" s="5" t="s">
-        <v>49</v>
+        <v>191</v>
       </c>
       <c r="T14" s="5" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="U14" s="5" t="s">
-        <v>49</v>
+        <v>191</v>
       </c>
       <c r="V14" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="W14" s="5" t="s">
-        <v>302</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="W14" s="5"/>
       <c r="X14" s="5"/>
       <c r="Y14" s="5" t="s">
         <v>51</v>
       </c>
       <c r="Z14" s="7">
-        <v>7030.24</v>
+        <v>6392.96</v>
       </c>
       <c r="AA14" s="7">
         <v>0</v>
@@ -9207,33 +9193,33 @@
         <v>0</v>
       </c>
       <c r="AC14" s="6">
-        <v>46204</v>
+        <v>46195</v>
       </c>
       <c r="AD14" s="7">
-        <v>7030.24</v>
+        <v>6392.96</v>
       </c>
       <c r="AE14" s="4">
         <v>72</v>
       </c>
       <c r="AF14" s="5" t="s">
-        <v>303</v>
+        <v>230</v>
       </c>
       <c r="AG14" s="5" t="s">
-        <v>304</v>
+        <v>211</v>
       </c>
       <c r="AH14" s="5" t="s">
-        <v>305</v>
+        <v>206</v>
       </c>
       <c r="AI14" s="5"/>
       <c r="AJ14" s="4"/>
       <c r="AK14" s="5" t="s">
-        <v>290</v>
+        <v>85</v>
       </c>
       <c r="AL14" s="5" t="s">
-        <v>291</v>
+        <v>243</v>
       </c>
       <c r="AM14" s="6">
-        <v>46199</v>
+        <v>46183</v>
       </c>
       <c r="AN14" s="5" t="s">
         <v>179</v>
@@ -9244,55 +9230,55 @@
         <v>87</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>308</v>
+        <v>244</v>
       </c>
       <c r="C15" s="3">
-        <v>46162</v>
+        <v>46156</v>
       </c>
       <c r="D15" s="4">
-        <v>559115746</v>
+        <v>559006292</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>309</v>
+        <v>245</v>
       </c>
       <c r="F15" s="6">
-        <v>46153</v>
+        <v>46147</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>310</v>
+        <v>246</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>310</v>
+        <v>246</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>171</v>
+        <v>247</v>
       </c>
       <c r="K15" s="3">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="L15" s="12">
         <f ca="1">IF($O15="","",$O15-TODAY())</f>
-        <v>-90</v>
+        <v>209</v>
       </c>
       <c r="M15" s="12">
         <f ca="1">IF($C15="","",$C15+365-TODAY())</f>
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="N15" s="12">
-        <f ca="1">IF($C15="","",$C15+90-TODAY())</f>
-        <v>-51</v>
+        <f ca="1">IF($C15="","",$C15+120-TODAY())</f>
+        <v>-27</v>
       </c>
       <c r="O15" s="6">
-        <v>46213</v>
+        <v>46512</v>
       </c>
       <c r="P15" s="5" t="s">
-        <v>144</v>
+        <v>50</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>311</v>
+        <v>121</v>
       </c>
       <c r="R15" s="5" t="s">
         <v>50</v>
@@ -9301,21 +9287,21 @@
         <v>49</v>
       </c>
       <c r="T15" s="5" t="s">
-        <v>46</v>
+        <v>103</v>
       </c>
       <c r="U15" s="5" t="s">
         <v>49</v>
       </c>
       <c r="V15" s="5" t="s">
-        <v>172</v>
+        <v>248</v>
       </c>
       <c r="W15" s="5"/>
       <c r="X15" s="5"/>
       <c r="Y15" s="5" t="s">
-        <v>173</v>
+        <v>51</v>
       </c>
       <c r="Z15" s="7">
-        <v>36353.800000000003</v>
+        <v>5320.49</v>
       </c>
       <c r="AA15" s="7">
         <v>0</v>
@@ -9324,26 +9310,26 @@
         <v>0</v>
       </c>
       <c r="AC15" s="6">
-        <v>46162</v>
+        <v>46156</v>
       </c>
       <c r="AD15" s="7">
-        <v>36353.800000000003</v>
+        <v>5320.49</v>
       </c>
       <c r="AE15" s="4">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AF15" s="5" t="s">
-        <v>174</v>
+        <v>249</v>
       </c>
       <c r="AG15" s="5"/>
       <c r="AH15" s="5"/>
       <c r="AI15" s="5"/>
       <c r="AJ15" s="4"/>
       <c r="AK15" s="5" t="s">
-        <v>312</v>
+        <v>250</v>
       </c>
       <c r="AL15" s="5" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="AM15" s="6">
         <v>46155</v>
@@ -9357,80 +9343,78 @@
         <v>87</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>316</v>
+        <v>265</v>
       </c>
       <c r="C16" s="3">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="D16" s="4">
-        <v>559005954</v>
+        <v>561877866</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>317</v>
+        <v>266</v>
       </c>
       <c r="F16" s="6">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="G16" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="I16" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="H16" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>44</v>
-      </c>
       <c r="J16" s="5" t="s">
-        <v>318</v>
+        <v>189</v>
       </c>
       <c r="K16" s="3">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="L16" s="12">
         <f ca="1">IF($O16="","",$O16-TODAY())</f>
-        <v>-67</v>
+        <v>212</v>
       </c>
       <c r="M16" s="12">
-        <f ca="1">IF($F16="","",$F16+90-TODAY())</f>
-        <v>-67</v>
+        <f ca="1">IF($C16="","",$C16+365-TODAY())</f>
+        <v>247</v>
       </c>
       <c r="N16" s="12">
-        <f ca="1">IF($C16="","",$C16+365-TODAY())</f>
-        <v>246</v>
+        <f ca="1">IF($C16="","",$C16+120-TODAY())</f>
+        <v>2</v>
       </c>
       <c r="O16" s="6">
-        <v>46236</v>
+        <v>46515</v>
       </c>
       <c r="P16" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="Q16" s="5" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="R16" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="S16" s="5" t="s">
-        <v>191</v>
+        <v>49</v>
       </c>
       <c r="T16" s="5" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="U16" s="5" t="s">
         <v>49</v>
       </c>
       <c r="V16" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="W16" s="5" t="s">
-        <v>319</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="W16" s="5"/>
       <c r="X16" s="5"/>
       <c r="Y16" s="5" t="s">
-        <v>51</v>
+        <v>192</v>
       </c>
       <c r="Z16" s="7">
-        <v>4520.1099999999997</v>
+        <v>72707.600000000006</v>
       </c>
       <c r="AA16" s="7">
         <v>0</v>
@@ -9439,29 +9423,33 @@
         <v>0</v>
       </c>
       <c r="AC16" s="6">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="AD16" s="7">
-        <v>4520.1099999999997</v>
+        <v>72707.600000000006</v>
       </c>
       <c r="AE16" s="4">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="AF16" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="AG16" s="5"/>
-      <c r="AH16" s="5"/>
+        <v>174</v>
+      </c>
+      <c r="AG16" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="AH16" s="5" t="s">
+        <v>267</v>
+      </c>
       <c r="AI16" s="5"/>
       <c r="AJ16" s="4"/>
       <c r="AK16" s="5" t="s">
-        <v>231</v>
+        <v>268</v>
       </c>
       <c r="AL16" s="5" t="s">
-        <v>68</v>
+        <v>269</v>
       </c>
       <c r="AM16" s="6">
-        <v>46157</v>
+        <v>46183</v>
       </c>
       <c r="AN16" s="5" t="s">
         <v>179</v>
@@ -9469,73 +9457,73 @@
     </row>
     <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>321</v>
+        <v>270</v>
       </c>
       <c r="C17" s="3">
-        <v>46224</v>
+        <v>46211</v>
       </c>
       <c r="D17" s="4">
-        <v>559736857</v>
+        <v>559783560</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>322</v>
+        <v>271</v>
       </c>
       <c r="F17" s="6">
-        <v>46150</v>
+        <v>46156</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>323</v>
+        <v>272</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>323</v>
+        <v>246</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>324</v>
+        <v>272</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>205</v>
+        <v>182</v>
       </c>
       <c r="K17" s="3">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="L17" s="12">
         <f ca="1">IF($O17="","",$O17-TODAY())</f>
-        <v>-63</v>
+        <v>218</v>
       </c>
       <c r="M17" s="12">
-        <f ca="1">IF($F17="","",$F17+90-TODAY())</f>
-        <v>-63</v>
+        <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
+        <v>273</v>
       </c>
       <c r="N17" s="12">
-        <f ca="1">IF($C17="","",$C17+180-TODAY())</f>
-        <v>101</v>
+        <f ca="1">IF($C17="","",$C17+120-TODAY())</f>
+        <v>28</v>
       </c>
       <c r="O17" s="6">
-        <v>46240</v>
+        <v>46521</v>
       </c>
       <c r="P17" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="Q17" s="5" t="s">
-        <v>325</v>
+        <v>121</v>
       </c>
       <c r="R17" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="S17" s="5" t="s">
-        <v>191</v>
+        <v>49</v>
       </c>
       <c r="T17" s="5" t="s">
-        <v>48</v>
+        <v>103</v>
       </c>
       <c r="U17" s="5" t="s">
         <v>49</v>
       </c>
       <c r="V17" s="5" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="W17" s="5"/>
       <c r="X17" s="5"/>
@@ -9549,31 +9537,33 @@
         <v>0</v>
       </c>
       <c r="AB17" s="7">
-        <v>0</v>
+        <v>176.56</v>
       </c>
       <c r="AC17" s="6">
-        <v>46224</v>
+        <v>46211</v>
       </c>
       <c r="AD17" s="7">
-        <v>5916.4</v>
+        <v>5739.84</v>
       </c>
       <c r="AE17" s="4">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="AF17" s="5" t="s">
         <v>174</v>
       </c>
       <c r="AG17" s="5" t="s">
-        <v>288</v>
+        <v>211</v>
       </c>
       <c r="AH17" s="5"/>
       <c r="AI17" s="5"/>
-      <c r="AJ17" s="4"/>
+      <c r="AJ17" s="4">
+        <v>562576876</v>
+      </c>
       <c r="AK17" s="5" t="s">
-        <v>312</v>
+        <v>263</v>
       </c>
       <c r="AL17" s="5" t="s">
-        <v>326</v>
+        <v>264</v>
       </c>
       <c r="AM17" s="6">
         <v>46162</v>
@@ -9584,81 +9574,83 @@
     </row>
     <row r="18" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>530</v>
+        <v>87</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>535</v>
+        <v>298</v>
       </c>
       <c r="C18" s="3">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="D18" s="4">
-        <v>562420138</v>
+        <v>563514079</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>336</v>
+        <v>299</v>
       </c>
       <c r="F18" s="6">
-        <v>46153</v>
+        <v>46170</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>131</v>
+        <v>246</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>131</v>
+        <v>246</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>44</v>
+        <v>300</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>329</v>
+        <v>301</v>
       </c>
       <c r="K18" s="3">
         <v>46255</v>
       </c>
       <c r="L18" s="12">
         <f ca="1">IF($O18="","",$O18-TODAY())</f>
-        <v>-60</v>
+        <v>232</v>
       </c>
       <c r="M18" s="12">
-        <f ca="1">IF($F18="","",$F18+90-TODAY())</f>
-        <v>-60</v>
+        <f ca="1">IF($C18="","",$C18+365-TODAY())</f>
+        <v>266</v>
       </c>
       <c r="N18" s="12">
-        <f ca="1">IF($C18="","",$C18+365-TODAY())</f>
-        <v>265</v>
+        <f ca="1">IF($C18="","",$C18+120-TODAY())</f>
+        <v>21</v>
       </c>
       <c r="O18" s="6">
-        <v>46243</v>
+        <v>46535</v>
       </c>
       <c r="P18" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="Q18" s="5" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="R18" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="S18" s="5" t="s">
-        <v>191</v>
+        <v>49</v>
       </c>
       <c r="T18" s="5" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="U18" s="5" t="s">
         <v>49</v>
       </c>
       <c r="V18" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="W18" s="5"/>
+        <v>248</v>
+      </c>
+      <c r="W18" s="5" t="s">
+        <v>302</v>
+      </c>
       <c r="X18" s="5"/>
       <c r="Y18" s="5" t="s">
-        <v>192</v>
+        <v>51</v>
       </c>
       <c r="Z18" s="7">
-        <v>11832.8</v>
+        <v>7030.24</v>
       </c>
       <c r="AA18" s="7">
         <v>0</v>
@@ -9667,33 +9659,33 @@
         <v>0</v>
       </c>
       <c r="AC18" s="6">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="AD18" s="7">
-        <v>11832.8</v>
+        <v>7030.24</v>
       </c>
       <c r="AE18" s="4">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="AF18" s="5" t="s">
-        <v>174</v>
+        <v>303</v>
       </c>
       <c r="AG18" s="5" t="s">
-        <v>225</v>
+        <v>304</v>
       </c>
       <c r="AH18" s="5" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="AI18" s="5"/>
       <c r="AJ18" s="4"/>
       <c r="AK18" s="5" t="s">
-        <v>81</v>
+        <v>290</v>
       </c>
       <c r="AL18" s="5" t="s">
-        <v>54</v>
+        <v>291</v>
       </c>
       <c r="AM18" s="6">
-        <v>46189</v>
+        <v>46199</v>
       </c>
       <c r="AN18" s="5" t="s">
         <v>179</v>
@@ -9704,60 +9696,78 @@
         <v>87</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>337</v>
+        <v>308</v>
       </c>
       <c r="C19" s="3">
-        <v>46168</v>
+        <v>46162</v>
       </c>
       <c r="D19" s="4">
-        <v>559748258</v>
+        <v>559115746</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>338</v>
+        <v>309</v>
       </c>
       <c r="F19" s="6">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>155</v>
+        <v>310</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>155</v>
+        <v>310</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>260</v>
+        <v>171</v>
       </c>
       <c r="K19" s="3">
-        <v>46244</v>
-      </c>
-      <c r="L19" s="12" t="str">
+        <v>46255</v>
+      </c>
+      <c r="L19" s="12">
         <f ca="1">IF($O19="","",$O19-TODAY())</f>
-        <v/>
-      </c>
-      <c r="M19" s="12"/>
-      <c r="N19" s="12"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="5"/>
+        <v>-90</v>
+      </c>
+      <c r="M19" s="12">
+        <f ca="1">IF($C19="","",$C19+365-TODAY())</f>
+        <v>224</v>
+      </c>
+      <c r="N19" s="12">
+        <f ca="1">IF($C19="","",$C19+90-TODAY())</f>
+        <v>-51</v>
+      </c>
+      <c r="O19" s="6">
+        <v>46213</v>
+      </c>
+      <c r="P19" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="Q19" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="R19" s="5"/>
-      <c r="S19" s="5"/>
-      <c r="T19" s="5"/>
-      <c r="U19" s="5"/>
+        <v>311</v>
+      </c>
+      <c r="R19" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="S19" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="T19" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="U19" s="5" t="s">
+        <v>49</v>
+      </c>
       <c r="V19" s="5" t="s">
-        <v>248</v>
+        <v>172</v>
       </c>
       <c r="W19" s="5"/>
       <c r="X19" s="5"/>
       <c r="Y19" s="5" t="s">
-        <v>51</v>
+        <v>173</v>
       </c>
       <c r="Z19" s="7">
-        <v>6392.96</v>
+        <v>36353.800000000003</v>
       </c>
       <c r="AA19" s="7">
         <v>0</v>
@@ -9765,28 +9775,30 @@
       <c r="AB19" s="7">
         <v>0</v>
       </c>
-      <c r="AC19" s="6"/>
+      <c r="AC19" s="6">
+        <v>46162</v>
+      </c>
       <c r="AD19" s="7">
-        <v>6392.96</v>
+        <v>36353.800000000003</v>
       </c>
       <c r="AE19" s="4">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="AF19" s="5" t="s">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="AG19" s="5"/>
       <c r="AH19" s="5"/>
       <c r="AI19" s="5"/>
       <c r="AJ19" s="4"/>
       <c r="AK19" s="5" t="s">
-        <v>76</v>
+        <v>312</v>
       </c>
       <c r="AL19" s="5" t="s">
-        <v>185</v>
+        <v>226</v>
       </c>
       <c r="AM19" s="6">
-        <v>46162</v>
+        <v>46155</v>
       </c>
       <c r="AN19" s="5" t="s">
         <v>179</v>
@@ -9797,60 +9809,80 @@
         <v>87</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>337</v>
+        <v>316</v>
       </c>
       <c r="C20" s="3">
-        <v>46171</v>
+        <v>46184</v>
       </c>
       <c r="D20" s="4">
-        <v>559795824</v>
+        <v>559005954</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>339</v>
+        <v>317</v>
       </c>
       <c r="F20" s="6">
-        <v>46149</v>
+        <v>46146</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>205</v>
+        <v>318</v>
       </c>
       <c r="K20" s="3">
-        <v>46244</v>
-      </c>
-      <c r="L20" s="12" t="str">
+        <v>46253</v>
+      </c>
+      <c r="L20" s="12">
         <f ca="1">IF($O20="","",$O20-TODAY())</f>
-        <v/>
-      </c>
-      <c r="M20" s="12"/>
-      <c r="N20" s="12"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="5"/>
+        <v>-67</v>
+      </c>
+      <c r="M20" s="12">
+        <f ca="1">IF($F20="","",$F20+90-TODAY())</f>
+        <v>-67</v>
+      </c>
+      <c r="N20" s="12">
+        <f ca="1">IF($C20="","",$C20+365-TODAY())</f>
+        <v>246</v>
+      </c>
+      <c r="O20" s="6">
+        <v>46236</v>
+      </c>
+      <c r="P20" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="Q20" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="R20" s="5"/>
-      <c r="S20" s="5"/>
-      <c r="T20" s="5"/>
-      <c r="U20" s="5"/>
+        <v>152</v>
+      </c>
+      <c r="R20" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="S20" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="T20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="U20" s="5" t="s">
+        <v>49</v>
+      </c>
       <c r="V20" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="W20" s="5"/>
+        <v>248</v>
+      </c>
+      <c r="W20" s="5" t="s">
+        <v>319</v>
+      </c>
       <c r="X20" s="5"/>
       <c r="Y20" s="5" t="s">
-        <v>173</v>
+        <v>51</v>
       </c>
       <c r="Z20" s="7">
-        <v>5916.4</v>
+        <v>4520.1099999999997</v>
       </c>
       <c r="AA20" s="7">
         <v>0</v>
@@ -9859,31 +9891,29 @@
         <v>0</v>
       </c>
       <c r="AC20" s="6">
-        <v>46171</v>
+        <v>46184</v>
       </c>
       <c r="AD20" s="7">
-        <v>5916.4</v>
+        <v>4520.1099999999997</v>
       </c>
       <c r="AE20" s="4">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AF20" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="AG20" s="5" t="s">
-        <v>206</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="AG20" s="5"/>
       <c r="AH20" s="5"/>
       <c r="AI20" s="5"/>
       <c r="AJ20" s="4"/>
       <c r="AK20" s="5" t="s">
-        <v>340</v>
+        <v>231</v>
       </c>
       <c r="AL20" s="5" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="AM20" s="6">
-        <v>46162</v>
+        <v>46157</v>
       </c>
       <c r="AN20" s="5" t="s">
         <v>179</v>
@@ -9891,67 +9921,67 @@
     </row>
     <row r="21" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>195</v>
+        <v>321</v>
       </c>
       <c r="C21" s="3">
-        <v>46183</v>
+        <v>46224</v>
       </c>
       <c r="D21" s="4">
-        <v>561237046</v>
+        <v>559736857</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>196</v>
+        <v>322</v>
       </c>
       <c r="F21" s="6">
-        <v>46163</v>
+        <v>46150</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>71</v>
+        <v>323</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>71</v>
+        <v>323</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>197</v>
+        <v>324</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="K21" s="3">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="L21" s="12">
         <f ca="1">IF($O21="","",$O21-TODAY())</f>
-        <v>-50</v>
+        <v>-63</v>
       </c>
       <c r="M21" s="12">
+        <f ca="1">IF($F21="","",$F21+90-TODAY())</f>
+        <v>-63</v>
+      </c>
+      <c r="N21" s="12">
         <f ca="1">IF($C21="","",$C21+180-TODAY())</f>
-        <v>60</v>
-      </c>
-      <c r="N21" s="12">
-        <f ca="1">IF($C21="","",$C21+365-TODAY())</f>
-        <v>245</v>
+        <v>101</v>
       </c>
       <c r="O21" s="6">
-        <v>46253</v>
+        <v>46240</v>
       </c>
       <c r="P21" s="5" t="s">
         <v>46</v>
       </c>
       <c r="Q21" s="5" t="s">
-        <v>73</v>
+        <v>325</v>
       </c>
       <c r="R21" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="S21" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="T21" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="S21" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="T21" s="5" t="s">
-        <v>50</v>
       </c>
       <c r="U21" s="5" t="s">
         <v>49</v>
@@ -9962,10 +9992,10 @@
       <c r="W21" s="5"/>
       <c r="X21" s="5"/>
       <c r="Y21" s="5" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="Z21" s="7">
-        <v>2958.2</v>
+        <v>5916.4</v>
       </c>
       <c r="AA21" s="7">
         <v>0</v>
@@ -9974,31 +10004,31 @@
         <v>0</v>
       </c>
       <c r="AC21" s="6">
-        <v>46183</v>
+        <v>46224</v>
       </c>
       <c r="AD21" s="7">
-        <v>2958.2</v>
+        <v>5916.4</v>
       </c>
       <c r="AE21" s="4">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="AF21" s="5" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="AG21" s="5" t="s">
-        <v>201</v>
+        <v>288</v>
       </c>
       <c r="AH21" s="5"/>
       <c r="AI21" s="5"/>
       <c r="AJ21" s="4"/>
       <c r="AK21" s="5" t="s">
-        <v>202</v>
+        <v>312</v>
       </c>
       <c r="AL21" s="5" t="s">
-        <v>54</v>
+        <v>326</v>
       </c>
       <c r="AM21" s="6">
-        <v>46177</v>
+        <v>46162</v>
       </c>
       <c r="AN21" s="5" t="s">
         <v>179</v>
@@ -10006,64 +10036,64 @@
     </row>
     <row r="22" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>115</v>
+        <v>530</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>203</v>
+        <v>535</v>
       </c>
       <c r="C22" s="3">
-        <v>46194</v>
+        <v>46203</v>
       </c>
       <c r="D22" s="4">
-        <v>561851402</v>
+        <v>562420138</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>204</v>
+        <v>336</v>
       </c>
       <c r="F22" s="6">
-        <v>46164</v>
+        <v>46153</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="I22" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>205</v>
+        <v>329</v>
       </c>
       <c r="K22" s="3">
-        <v>46245</v>
+        <v>46255</v>
       </c>
       <c r="L22" s="12">
         <f ca="1">IF($O22="","",$O22-TODAY())</f>
-        <v>-49</v>
+        <v>-60</v>
       </c>
       <c r="M22" s="12">
-        <f ca="1">IF($C22="","",$C22+365-TODAY())</f>
-        <v>256</v>
+        <f ca="1">IF($F22="","",$F22+90-TODAY())</f>
+        <v>-60</v>
       </c>
       <c r="N22" s="12">
         <f ca="1">IF($C22="","",$C22+365-TODAY())</f>
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="O22" s="6">
-        <v>46254</v>
+        <v>46243</v>
       </c>
       <c r="P22" s="5" t="s">
         <v>46</v>
       </c>
       <c r="Q22" s="5" t="s">
-        <v>96</v>
+        <v>152</v>
       </c>
       <c r="R22" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="S22" s="5" t="s">
-        <v>49</v>
+        <v>191</v>
       </c>
       <c r="T22" s="5" t="s">
         <v>50</v>
@@ -10072,15 +10102,15 @@
         <v>49</v>
       </c>
       <c r="V22" s="5" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="W22" s="5"/>
       <c r="X22" s="5"/>
       <c r="Y22" s="5" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="Z22" s="7">
-        <v>36353.800000000003</v>
+        <v>11832.8</v>
       </c>
       <c r="AA22" s="7">
         <v>0</v>
@@ -10089,31 +10119,33 @@
         <v>0</v>
       </c>
       <c r="AC22" s="6">
-        <v>46194</v>
+        <v>46203</v>
       </c>
       <c r="AD22" s="7">
-        <v>36353.800000000003</v>
+        <v>11832.8</v>
       </c>
       <c r="AE22" s="4">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AF22" s="5" t="s">
         <v>174</v>
       </c>
       <c r="AG22" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="AH22" s="5"/>
+        <v>225</v>
+      </c>
+      <c r="AH22" s="5" t="s">
+        <v>282</v>
+      </c>
       <c r="AI22" s="5"/>
       <c r="AJ22" s="4"/>
       <c r="AK22" s="5" t="s">
-        <v>207</v>
+        <v>81</v>
       </c>
       <c r="AL22" s="5" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="AM22" s="6">
-        <v>46183</v>
+        <v>46189</v>
       </c>
       <c r="AN22" s="5" t="s">
         <v>179</v>
@@ -10121,81 +10153,63 @@
     </row>
     <row r="23" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>208</v>
+        <v>337</v>
       </c>
       <c r="C23" s="3">
-        <v>46191</v>
+        <v>46168</v>
       </c>
       <c r="D23" s="4">
-        <v>561860576</v>
+        <v>559748258</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>209</v>
+        <v>338</v>
       </c>
       <c r="F23" s="6">
-        <v>46168</v>
+        <v>46146</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>43</v>
+        <v>155</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>43</v>
+        <v>155</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="K23" s="3">
-        <v>46248</v>
-      </c>
-      <c r="L23" s="12">
+        <v>46244</v>
+      </c>
+      <c r="L23" s="12" t="str">
         <f ca="1">IF($O23="","",$O23-TODAY())</f>
-        <v>-45</v>
-      </c>
-      <c r="M23" s="12">
-        <f ca="1">IF($C23="","",$C23+180-TODAY())</f>
-        <v>68</v>
-      </c>
-      <c r="N23" s="12">
-        <f ca="1">IF($C23="","",$C23+365-TODAY())</f>
-        <v>253</v>
-      </c>
-      <c r="O23" s="6">
-        <v>46258</v>
-      </c>
-      <c r="P23" s="5" t="s">
-        <v>46</v>
-      </c>
+        <v/>
+      </c>
+      <c r="M23" s="12"/>
+      <c r="N23" s="12"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="5"/>
       <c r="Q23" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="R23" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="S23" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="T23" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="U23" s="5" t="s">
-        <v>49</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="R23" s="5"/>
+      <c r="S23" s="5"/>
+      <c r="T23" s="5"/>
+      <c r="U23" s="5"/>
       <c r="V23" s="5" t="s">
-        <v>183</v>
+        <v>248</v>
       </c>
       <c r="W23" s="5"/>
       <c r="X23" s="5"/>
       <c r="Y23" s="5" t="s">
-        <v>199</v>
+        <v>51</v>
       </c>
       <c r="Z23" s="7">
-        <v>2958.2</v>
+        <v>6392.96</v>
       </c>
       <c r="AA23" s="7">
         <v>0</v>
@@ -10203,34 +10217,28 @@
       <c r="AB23" s="7">
         <v>0</v>
       </c>
-      <c r="AC23" s="6">
-        <v>46191</v>
-      </c>
+      <c r="AC23" s="6"/>
       <c r="AD23" s="7">
-        <v>2958.2</v>
+        <v>6392.96</v>
       </c>
       <c r="AE23" s="4">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AF23" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="AG23" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="AH23" s="5" t="s">
-        <v>212</v>
-      </c>
+      <c r="AG23" s="5"/>
+      <c r="AH23" s="5"/>
       <c r="AI23" s="5"/>
       <c r="AJ23" s="4"/>
       <c r="AK23" s="5" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="AL23" s="5" t="s">
-        <v>213</v>
+        <v>185</v>
       </c>
       <c r="AM23" s="6">
-        <v>46183</v>
+        <v>46162</v>
       </c>
       <c r="AN23" s="5" t="s">
         <v>179</v>
@@ -10238,74 +10246,63 @@
     </row>
     <row r="24" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>214</v>
+        <v>337</v>
       </c>
       <c r="C24" s="3">
-        <v>46223</v>
+        <v>46171</v>
       </c>
       <c r="D24" s="4">
-        <v>559770046</v>
+        <v>559795824</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>215</v>
+        <v>339</v>
       </c>
       <c r="F24" s="6">
-        <v>46146</v>
+        <v>46149</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>216</v>
+        <v>155</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>216</v>
+        <v>155</v>
       </c>
       <c r="I24" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="K24" s="3">
-        <v>46248</v>
-      </c>
-      <c r="L24" s="12">
+        <v>46244</v>
+      </c>
+      <c r="L24" s="12" t="str">
         <f ca="1">IF($O24="","",$O24-TODAY())</f>
-        <v>-37</v>
+        <v/>
       </c>
       <c r="M24" s="12"/>
-      <c r="N24" s="12">
-        <f ca="1">IF($C24="","",$C24+65-TODAY())</f>
-        <v>-15</v>
-      </c>
-      <c r="O24" s="6">
-        <v>46266</v>
-      </c>
-      <c r="P24" s="5" t="s">
-        <v>103</v>
-      </c>
+      <c r="N24" s="12"/>
+      <c r="O24" s="6"/>
+      <c r="P24" s="5"/>
       <c r="Q24" s="5" t="s">
-        <v>217</v>
+        <v>156</v>
       </c>
       <c r="R24" s="5"/>
       <c r="S24" s="5"/>
-      <c r="T24" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="U24" s="5" t="s">
-        <v>49</v>
-      </c>
+      <c r="T24" s="5"/>
+      <c r="U24" s="5"/>
       <c r="V24" s="5" t="s">
         <v>172</v>
       </c>
       <c r="W24" s="5"/>
       <c r="X24" s="5"/>
       <c r="Y24" s="5" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="Z24" s="7">
-        <v>2958.2</v>
+        <v>5916.4</v>
       </c>
       <c r="AA24" s="7">
         <v>0</v>
@@ -10314,26 +10311,28 @@
         <v>0</v>
       </c>
       <c r="AC24" s="6">
-        <v>46223</v>
+        <v>46171</v>
       </c>
       <c r="AD24" s="7">
-        <v>2958.2</v>
+        <v>5916.4</v>
       </c>
       <c r="AE24" s="4">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="AF24" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="AG24" s="5"/>
+      <c r="AG24" s="5" t="s">
+        <v>206</v>
+      </c>
       <c r="AH24" s="5"/>
       <c r="AI24" s="5"/>
       <c r="AJ24" s="4"/>
       <c r="AK24" s="5" t="s">
-        <v>100</v>
+        <v>340</v>
       </c>
       <c r="AL24" s="5" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="AM24" s="6">
         <v>46162</v>
@@ -10344,65 +10343,67 @@
     </row>
     <row r="25" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="C25" s="3">
-        <v>46249</v>
+        <v>46183</v>
       </c>
       <c r="D25" s="4">
-        <v>559009959</v>
+        <v>561237046</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>253</v>
+        <v>196</v>
       </c>
       <c r="F25" s="6">
-        <v>46147</v>
+        <v>46163</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>246</v>
+        <v>71</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>246</v>
+        <v>71</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>44</v>
+        <v>197</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="K25" s="3"/>
+      <c r="K25" s="3">
+        <v>46245</v>
+      </c>
       <c r="L25" s="12">
         <f ca="1">IF($O25="","",$O25-TODAY())</f>
-        <v>209</v>
+        <v>-50</v>
       </c>
       <c r="M25" s="12">
+        <f ca="1">IF($C25="","",$C25+180-TODAY())</f>
+        <v>60</v>
+      </c>
+      <c r="N25" s="12">
         <f ca="1">IF($C25="","",$C25+365-TODAY())</f>
-        <v>311</v>
-      </c>
-      <c r="N25" s="12">
-        <f ca="1">IF($C25="","",$C25+120-TODAY())</f>
-        <v>66</v>
+        <v>245</v>
       </c>
       <c r="O25" s="6">
-        <v>46512</v>
+        <v>46253</v>
       </c>
       <c r="P25" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="Q25" s="5" t="s">
-        <v>121</v>
+        <v>73</v>
       </c>
       <c r="R25" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S25" s="5" t="s">
         <v>49</v>
       </c>
       <c r="T25" s="5" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="U25" s="5" t="s">
         <v>49</v>
@@ -10422,34 +10423,34 @@
         <v>0</v>
       </c>
       <c r="AB25" s="7">
-        <v>88.28</v>
+        <v>0</v>
       </c>
       <c r="AC25" s="6">
-        <v>46197</v>
+        <v>46183</v>
       </c>
       <c r="AD25" s="7">
-        <v>2869.92</v>
+        <v>2958.2</v>
       </c>
       <c r="AE25" s="4">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="AF25" s="5" t="s">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="AG25" s="5" t="s">
-        <v>254</v>
+        <v>201</v>
       </c>
       <c r="AH25" s="5"/>
       <c r="AI25" s="5"/>
       <c r="AJ25" s="4"/>
       <c r="AK25" s="5" t="s">
-        <v>255</v>
+        <v>202</v>
       </c>
       <c r="AL25" s="5" t="s">
-        <v>256</v>
+        <v>54</v>
       </c>
       <c r="AM25" s="6">
-        <v>46155</v>
+        <v>46177</v>
       </c>
       <c r="AN25" s="5" t="s">
         <v>179</v>
@@ -10457,56 +10458,58 @@
     </row>
     <row r="26" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>257</v>
+        <v>203</v>
       </c>
       <c r="C26" s="3">
-        <v>46202</v>
+        <v>46194</v>
       </c>
       <c r="D26" s="4">
-        <v>559008757</v>
+        <v>561851402</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>258</v>
+        <v>204</v>
       </c>
       <c r="F26" s="6">
-        <v>46150</v>
+        <v>46164</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>259</v>
+        <v>95</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>246</v>
+        <v>95</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>259</v>
+        <v>44</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="K26" s="3"/>
+        <v>205</v>
+      </c>
+      <c r="K26" s="3">
+        <v>46245</v>
+      </c>
       <c r="L26" s="12">
         <f ca="1">IF($O26="","",$O26-TODAY())</f>
-        <v>212</v>
+        <v>-49</v>
       </c>
       <c r="M26" s="12">
         <f ca="1">IF($C26="","",$C26+365-TODAY())</f>
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="N26" s="12">
-        <f ca="1">IF($C26="","",$C26+120-TODAY())</f>
-        <v>19</v>
+        <f ca="1">IF($C26="","",$C26+365-TODAY())</f>
+        <v>256</v>
       </c>
       <c r="O26" s="6">
-        <v>46515</v>
+        <v>46254</v>
       </c>
       <c r="P26" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="Q26" s="5" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="R26" s="5" t="s">
         <v>50</v>
@@ -10515,56 +10518,54 @@
         <v>49</v>
       </c>
       <c r="T26" s="5" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="U26" s="5" t="s">
         <v>49</v>
       </c>
       <c r="V26" s="5" t="s">
-        <v>248</v>
+        <v>172</v>
       </c>
       <c r="W26" s="5"/>
       <c r="X26" s="5"/>
       <c r="Y26" s="5" t="s">
-        <v>51</v>
+        <v>173</v>
       </c>
       <c r="Z26" s="7">
-        <v>6392.96</v>
+        <v>36353.800000000003</v>
       </c>
       <c r="AA26" s="7">
-        <v>5624.17</v>
+        <v>0</v>
       </c>
       <c r="AB26" s="7">
-        <v>612.53</v>
+        <v>0</v>
       </c>
       <c r="AC26" s="6">
-        <v>46202</v>
+        <v>46194</v>
       </c>
       <c r="AD26" s="7">
-        <v>156.26</v>
+        <v>36353.800000000003</v>
       </c>
       <c r="AE26" s="4">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="AF26" s="5" t="s">
-        <v>261</v>
+        <v>174</v>
       </c>
       <c r="AG26" s="5" t="s">
-        <v>262</v>
+        <v>206</v>
       </c>
       <c r="AH26" s="5"/>
       <c r="AI26" s="5"/>
-      <c r="AJ26" s="4">
-        <v>564922724</v>
-      </c>
+      <c r="AJ26" s="4"/>
       <c r="AK26" s="5" t="s">
-        <v>263</v>
+        <v>207</v>
       </c>
       <c r="AL26" s="5" t="s">
-        <v>264</v>
+        <v>86</v>
       </c>
       <c r="AM26" s="6">
-        <v>46155</v>
+        <v>46183</v>
       </c>
       <c r="AN26" s="5" t="s">
         <v>179</v>
@@ -10575,80 +10576,78 @@
         <v>115</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>273</v>
+        <v>208</v>
       </c>
       <c r="C27" s="3">
-        <v>46247</v>
+        <v>46191</v>
       </c>
       <c r="D27" s="4">
-        <v>564572924</v>
+        <v>561860576</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>274</v>
+        <v>209</v>
       </c>
       <c r="F27" s="6">
-        <v>46156</v>
+        <v>46168</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>246</v>
+        <v>43</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>246</v>
+        <v>43</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>275</v>
+        <v>44</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>276</v>
+        <v>210</v>
       </c>
       <c r="K27" s="3">
-        <v>46254</v>
+        <v>46248</v>
       </c>
       <c r="L27" s="12">
         <f ca="1">IF($O27="","",$O27-TODAY())</f>
-        <v>218</v>
+        <v>-45</v>
       </c>
       <c r="M27" s="12">
+        <f ca="1">IF($C27="","",$C27+180-TODAY())</f>
+        <v>68</v>
+      </c>
+      <c r="N27" s="12">
         <f ca="1">IF($C27="","",$C27+365-TODAY())</f>
-        <v>309</v>
-      </c>
-      <c r="N27" s="12">
-        <f ca="1">IF($C27="","",$C27+120-TODAY())</f>
-        <v>64</v>
+        <v>253</v>
       </c>
       <c r="O27" s="6">
-        <v>46521</v>
+        <v>46258</v>
       </c>
       <c r="P27" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="Q27" s="5" t="s">
-        <v>121</v>
+        <v>47</v>
       </c>
       <c r="R27" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S27" s="5" t="s">
         <v>49</v>
       </c>
       <c r="T27" s="5" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="U27" s="5" t="s">
         <v>49</v>
       </c>
       <c r="V27" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="W27" s="5" t="s">
-        <v>277</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="W27" s="5"/>
       <c r="X27" s="5"/>
       <c r="Y27" s="5" t="s">
-        <v>51</v>
+        <v>199</v>
       </c>
       <c r="Z27" s="7">
-        <v>9040.2199999999993</v>
+        <v>2958.2</v>
       </c>
       <c r="AA27" s="7">
         <v>0</v>
@@ -10656,30 +10655,34 @@
       <c r="AB27" s="7">
         <v>0</v>
       </c>
-      <c r="AC27" s="6"/>
+      <c r="AC27" s="6">
+        <v>46191</v>
+      </c>
       <c r="AD27" s="7">
-        <v>9040.2199999999993</v>
+        <v>2958.2</v>
       </c>
       <c r="AE27" s="4">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="AF27" s="5" t="s">
-        <v>278</v>
+        <v>174</v>
       </c>
       <c r="AG27" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="AH27" s="5"/>
+        <v>211</v>
+      </c>
+      <c r="AH27" s="5" t="s">
+        <v>212</v>
+      </c>
       <c r="AI27" s="5"/>
       <c r="AJ27" s="4"/>
       <c r="AK27" s="5" t="s">
-        <v>255</v>
+        <v>100</v>
       </c>
       <c r="AL27" s="5" t="s">
-        <v>256</v>
+        <v>213</v>
       </c>
       <c r="AM27" s="6">
-        <v>46210</v>
+        <v>46183</v>
       </c>
       <c r="AN27" s="5" t="s">
         <v>179</v>
@@ -10690,78 +10693,71 @@
         <v>115</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>280</v>
+        <v>214</v>
       </c>
       <c r="C28" s="3">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="D28" s="4">
-        <v>559739970</v>
+        <v>559770046</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>281</v>
+        <v>215</v>
       </c>
       <c r="F28" s="6">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>246</v>
+        <v>216</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>246</v>
+        <v>216</v>
       </c>
       <c r="I28" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>260</v>
+        <v>198</v>
       </c>
       <c r="K28" s="3">
-        <v>46255</v>
+        <v>46248</v>
       </c>
       <c r="L28" s="12">
         <f ca="1">IF($O28="","",$O28-TODAY())</f>
-        <v>222</v>
-      </c>
-      <c r="M28" s="12">
-        <f ca="1">IF($C28="","",$C28+365-TODAY())</f>
-        <v>281</v>
-      </c>
+        <v>-37</v>
+      </c>
+      <c r="M28" s="12"/>
       <c r="N28" s="12">
-        <f ca="1">IF($C28="","",$C28+120-TODAY())</f>
-        <v>36</v>
+        <f ca="1">IF($C28="","",$C28+65-TODAY())</f>
+        <v>-15</v>
       </c>
       <c r="O28" s="6">
-        <v>46525</v>
+        <v>46266</v>
       </c>
       <c r="P28" s="5" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="Q28" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="R28" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="S28" s="5" t="s">
-        <v>49</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="R28" s="5"/>
+      <c r="S28" s="5"/>
       <c r="T28" s="5" t="s">
-        <v>103</v>
+        <v>218</v>
       </c>
       <c r="U28" s="5" t="s">
         <v>49</v>
       </c>
       <c r="V28" s="5" t="s">
-        <v>248</v>
+        <v>172</v>
       </c>
       <c r="W28" s="5"/>
       <c r="X28" s="5"/>
       <c r="Y28" s="5" t="s">
-        <v>51</v>
+        <v>199</v>
       </c>
       <c r="Z28" s="7">
-        <v>6392.96</v>
+        <v>2958.2</v>
       </c>
       <c r="AA28" s="7">
         <v>0</v>
@@ -10770,26 +10766,26 @@
         <v>0</v>
       </c>
       <c r="AC28" s="6">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="AD28" s="7">
-        <v>6392.96</v>
+        <v>2958.2</v>
       </c>
       <c r="AE28" s="4">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="AF28" s="5" t="s">
-        <v>282</v>
+        <v>174</v>
       </c>
       <c r="AG28" s="5"/>
       <c r="AH28" s="5"/>
       <c r="AI28" s="5"/>
       <c r="AJ28" s="4"/>
       <c r="AK28" s="5" t="s">
-        <v>283</v>
+        <v>100</v>
       </c>
       <c r="AL28" s="5" t="s">
-        <v>284</v>
+        <v>54</v>
       </c>
       <c r="AM28" s="6">
         <v>46162</v>
@@ -10803,19 +10799,19 @@
         <v>115</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="C29" s="3">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="D29" s="4">
-        <v>559735530</v>
+        <v>564572924</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="F29" s="6">
-        <v>46161</v>
+        <v>46156</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>246</v>
@@ -10824,28 +10820,28 @@
         <v>246</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>125</v>
+        <v>275</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="K29" s="3">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="L29" s="12">
         <f ca="1">IF($O29="","",$O29-TODAY())</f>
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="M29" s="12">
         <f ca="1">IF($C29="","",$C29+365-TODAY())</f>
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N29" s="12">
         <f ca="1">IF($C29="","",$C29+120-TODAY())</f>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O29" s="6">
-        <v>46526</v>
+        <v>46521</v>
       </c>
       <c r="P29" s="5" t="s">
         <v>50</v>
@@ -10868,13 +10864,15 @@
       <c r="V29" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="W29" s="5"/>
+      <c r="W29" s="5" t="s">
+        <v>277</v>
+      </c>
       <c r="X29" s="5"/>
       <c r="Y29" s="5" t="s">
         <v>51</v>
       </c>
       <c r="Z29" s="7">
-        <v>6392.96</v>
+        <v>9040.2199999999993</v>
       </c>
       <c r="AA29" s="7">
         <v>0</v>
@@ -10884,30 +10882,28 @@
       </c>
       <c r="AC29" s="6"/>
       <c r="AD29" s="7">
-        <v>6392.96</v>
+        <v>9040.2199999999993</v>
       </c>
       <c r="AE29" s="4">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="AF29" s="5" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="AG29" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="AH29" s="5" t="s">
-        <v>289</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="AH29" s="5"/>
       <c r="AI29" s="5"/>
       <c r="AJ29" s="4"/>
       <c r="AK29" s="5" t="s">
-        <v>290</v>
+        <v>255</v>
       </c>
       <c r="AL29" s="5" t="s">
-        <v>291</v>
+        <v>256</v>
       </c>
       <c r="AM29" s="6">
-        <v>46183</v>
+        <v>46210</v>
       </c>
       <c r="AN29" s="5" t="s">
         <v>179</v>
@@ -10915,22 +10911,22 @@
     </row>
     <row r="30" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="C30" s="3">
-        <v>46209</v>
+        <v>46219</v>
       </c>
       <c r="D30" s="4">
-        <v>561853521</v>
+        <v>559739970</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="F30" s="6">
-        <v>46168</v>
+        <v>46160</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>246</v>
@@ -10939,26 +10935,28 @@
         <v>246</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>294</v>
+        <v>44</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="K30" s="3"/>
+        <v>260</v>
+      </c>
+      <c r="K30" s="3">
+        <v>46255</v>
+      </c>
       <c r="L30" s="12">
         <f ca="1">IF($O30="","",$O30-TODAY())</f>
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="M30" s="12">
         <f ca="1">IF($C30="","",$C30+365-TODAY())</f>
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="N30" s="12">
         <f ca="1">IF($C30="","",$C30+120-TODAY())</f>
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="O30" s="6">
-        <v>46533</v>
+        <v>46525</v>
       </c>
       <c r="P30" s="5" t="s">
         <v>50</v>
@@ -10979,48 +10977,46 @@
         <v>49</v>
       </c>
       <c r="V30" s="5" t="s">
-        <v>172</v>
+        <v>248</v>
       </c>
       <c r="W30" s="5"/>
       <c r="X30" s="5"/>
       <c r="Y30" s="5" t="s">
-        <v>199</v>
+        <v>51</v>
       </c>
       <c r="Z30" s="7">
-        <v>18176.900000000001</v>
+        <v>6392.96</v>
       </c>
       <c r="AA30" s="7">
         <v>0</v>
       </c>
       <c r="AB30" s="7">
-        <v>542.44000000000005</v>
+        <v>0</v>
       </c>
       <c r="AC30" s="6">
-        <v>46209</v>
+        <v>46219</v>
       </c>
       <c r="AD30" s="7">
-        <v>17634.46</v>
+        <v>6392.96</v>
       </c>
       <c r="AE30" s="4">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AF30" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="AG30" s="5" t="s">
-        <v>296</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="AG30" s="5"/>
       <c r="AH30" s="5"/>
       <c r="AI30" s="5"/>
       <c r="AJ30" s="4"/>
       <c r="AK30" s="5" t="s">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="AL30" s="5" t="s">
-        <v>256</v>
+        <v>284</v>
       </c>
       <c r="AM30" s="6">
-        <v>46183</v>
+        <v>46162</v>
       </c>
       <c r="AN30" s="5" t="s">
         <v>179</v>
@@ -11028,22 +11024,22 @@
     </row>
     <row r="31" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="C31" s="3">
-        <v>46249</v>
+        <v>46246</v>
       </c>
       <c r="D31" s="4">
-        <v>561856360</v>
+        <v>559735530</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="F31" s="6">
-        <v>46168</v>
+        <v>46161</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>246</v>
@@ -11052,26 +11048,28 @@
         <v>246</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>272</v>
+        <v>125</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="K31" s="3"/>
+        <v>260</v>
+      </c>
+      <c r="K31" s="3">
+        <v>46255</v>
+      </c>
       <c r="L31" s="12">
         <f ca="1">IF($O31="","",$O31-TODAY())</f>
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="M31" s="12">
         <f ca="1">IF($C31="","",$C31+365-TODAY())</f>
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="N31" s="12">
         <f ca="1">IF($C31="","",$C31+120-TODAY())</f>
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O31" s="6">
-        <v>46533</v>
+        <v>46526</v>
       </c>
       <c r="P31" s="5" t="s">
         <v>50</v>
@@ -11092,15 +11090,15 @@
         <v>49</v>
       </c>
       <c r="V31" s="5" t="s">
-        <v>172</v>
+        <v>248</v>
       </c>
       <c r="W31" s="5"/>
       <c r="X31" s="5"/>
       <c r="Y31" s="5" t="s">
-        <v>199</v>
+        <v>51</v>
       </c>
       <c r="Z31" s="7">
-        <v>2958.2</v>
+        <v>6392.96</v>
       </c>
       <c r="AA31" s="7">
         <v>0</v>
@@ -11110,25 +11108,27 @@
       </c>
       <c r="AC31" s="6"/>
       <c r="AD31" s="7">
-        <v>2958.2</v>
+        <v>6392.96</v>
       </c>
       <c r="AE31" s="4">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AF31" s="5" t="s">
-        <v>174</v>
+        <v>287</v>
       </c>
       <c r="AG31" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="AH31" s="5"/>
+      <c r="AH31" s="5" t="s">
+        <v>289</v>
+      </c>
       <c r="AI31" s="5"/>
       <c r="AJ31" s="4"/>
       <c r="AK31" s="5" t="s">
-        <v>255</v>
+        <v>290</v>
       </c>
       <c r="AL31" s="5" t="s">
-        <v>256</v>
+        <v>291</v>
       </c>
       <c r="AM31" s="6">
         <v>46183</v>
@@ -12960,79 +12960,61 @@
     </row>
     <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>379</v>
+        <v>445</v>
       </c>
       <c r="C3" s="3">
-        <v>46170</v>
+        <v>46168</v>
       </c>
       <c r="D3" s="4">
-        <v>559356030</v>
+        <v>558845008</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>380</v>
+        <v>339</v>
       </c>
       <c r="F3" s="6">
-        <v>46156</v>
+        <v>46146</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>323</v>
+        <v>155</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>323</v>
+        <v>155</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="K3" s="3">
-        <v>46247</v>
-      </c>
-      <c r="L3" s="12">
+        <v>430</v>
+      </c>
+      <c r="K3" s="3"/>
+      <c r="L3" s="12" t="str">
         <f ca="1">IF($O3="","",$O3-TODAY())</f>
-        <v>-57</v>
-      </c>
-      <c r="M3" s="12">
-        <f ca="1">IF($F3="","",$F3+90-TODAY())</f>
-        <v>-57</v>
-      </c>
-      <c r="N3" s="12">
-        <f ca="1">IF($C3="","",$C3+180-TODAY())</f>
-        <v>47</v>
-      </c>
-      <c r="O3" s="6">
-        <v>46246</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>46</v>
-      </c>
+        <v/>
+      </c>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="5"/>
       <c r="Q3" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="R3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="T3" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="U3" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="V3" s="5"/>
+        <v>156</v>
+      </c>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5" t="s">
+        <v>319</v>
+      </c>
       <c r="W3" s="5"/>
       <c r="X3" s="5"/>
       <c r="Y3" s="5" t="s">
         <v>51</v>
       </c>
       <c r="Z3" s="7">
-        <v>7623.07</v>
+        <v>5614.63</v>
       </c>
       <c r="AA3" s="7">
         <v>0</v>
@@ -13040,30 +13022,28 @@
       <c r="AB3" s="7">
         <v>0</v>
       </c>
-      <c r="AC3" s="6">
-        <v>46170</v>
-      </c>
+      <c r="AC3" s="6"/>
       <c r="AD3" s="7">
-        <v>7623.07</v>
+        <v>5614.63</v>
       </c>
       <c r="AE3" s="4">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="AF3" s="5" t="s">
-        <v>288</v>
+        <v>206</v>
       </c>
       <c r="AG3" s="5"/>
       <c r="AH3" s="5"/>
       <c r="AI3" s="5"/>
       <c r="AJ3" s="4"/>
       <c r="AK3" s="5" t="s">
-        <v>162</v>
+        <v>207</v>
       </c>
       <c r="AL3" s="5" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="AM3" s="6">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="AN3" s="5" t="s">
         <v>382</v>
@@ -13074,64 +13054,64 @@
         <v>87</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C4" s="3">
-        <v>46252</v>
+        <v>46170</v>
       </c>
       <c r="D4" s="4">
-        <v>561233259</v>
+        <v>559356030</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="F4" s="6">
-        <v>46160</v>
+        <v>46156</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>43</v>
+        <v>323</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>43</v>
+        <v>323</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="K4" s="3">
-        <v>46252</v>
+        <v>46247</v>
       </c>
       <c r="L4" s="12">
         <f ca="1">IF($O4="","",$O4-TODAY())</f>
-        <v>-53</v>
+        <v>-57</v>
       </c>
       <c r="M4" s="12">
+        <f ca="1">IF($F4="","",$F4+90-TODAY())</f>
+        <v>-57</v>
+      </c>
+      <c r="N4" s="12">
         <f ca="1">IF($C4="","",$C4+180-TODAY())</f>
-        <v>129</v>
-      </c>
-      <c r="N4" s="12">
-        <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
-        <v>314</v>
+        <v>47</v>
       </c>
       <c r="O4" s="6">
-        <v>46250</v>
+        <v>46246</v>
       </c>
       <c r="P4" s="5" t="s">
         <v>46</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>47</v>
+        <v>325</v>
       </c>
       <c r="R4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="S4" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="T4" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="S4" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="T4" s="5" t="s">
-        <v>50</v>
       </c>
       <c r="U4" s="5" t="s">
         <v>49</v>
@@ -13143,7 +13123,7 @@
         <v>51</v>
       </c>
       <c r="Z4" s="7">
-        <v>9056.39</v>
+        <v>7623.07</v>
       </c>
       <c r="AA4" s="7">
         <v>0</v>
@@ -13151,32 +13131,30 @@
       <c r="AB4" s="7">
         <v>0</v>
       </c>
-      <c r="AC4" s="6"/>
+      <c r="AC4" s="6">
+        <v>46170</v>
+      </c>
       <c r="AD4" s="7">
-        <v>9056.39</v>
+        <v>7623.07</v>
       </c>
       <c r="AE4" s="4">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="AF4" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="AG4" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="AH4" s="5" t="s">
-        <v>386</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="AG4" s="5"/>
+      <c r="AH4" s="5"/>
       <c r="AI4" s="5"/>
       <c r="AJ4" s="4"/>
       <c r="AK4" s="5" t="s">
-        <v>387</v>
+        <v>162</v>
       </c>
       <c r="AL4" s="5" t="s">
         <v>357</v>
       </c>
       <c r="AM4" s="6">
-        <v>46177</v>
+        <v>46160</v>
       </c>
       <c r="AN4" s="5" t="s">
         <v>382</v>
@@ -13187,55 +13165,55 @@
         <v>87</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="C5" s="3">
-        <v>46242</v>
+        <v>46252</v>
       </c>
       <c r="D5" s="4">
-        <v>561246589</v>
+        <v>561233259</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="F5" s="6">
-        <v>46163</v>
+        <v>46160</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="K5" s="3">
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="L5" s="12">
         <f ca="1">IF($O5="","",$O5-TODAY())</f>
-        <v>-50</v>
+        <v>-53</v>
       </c>
       <c r="M5" s="12">
         <f ca="1">IF($C5="","",$C5+180-TODAY())</f>
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="N5" s="12">
         <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="O5" s="6">
-        <v>46253</v>
+        <v>46250</v>
       </c>
       <c r="P5" s="5" t="s">
         <v>46</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="R5" s="5" t="s">
         <v>48</v>
@@ -13249,16 +13227,14 @@
       <c r="U5" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="V5" s="5" t="s">
-        <v>319</v>
-      </c>
+      <c r="V5" s="5"/>
       <c r="W5" s="5"/>
       <c r="X5" s="5"/>
       <c r="Y5" s="5" t="s">
         <v>51</v>
       </c>
       <c r="Z5" s="7">
-        <v>6297.27</v>
+        <v>9056.39</v>
       </c>
       <c r="AA5" s="7">
         <v>0</v>
@@ -13266,28 +13242,26 @@
       <c r="AB5" s="7">
         <v>0</v>
       </c>
-      <c r="AC5" s="6">
-        <v>46183</v>
-      </c>
+      <c r="AC5" s="6"/>
       <c r="AD5" s="7">
-        <v>6297.27</v>
+        <v>9056.39</v>
       </c>
       <c r="AE5" s="4">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF5" s="5" t="s">
-        <v>394</v>
+        <v>211</v>
       </c>
       <c r="AG5" s="5" t="s">
-        <v>282</v>
+        <v>249</v>
       </c>
       <c r="AH5" s="5" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="AI5" s="5"/>
       <c r="AJ5" s="4"/>
       <c r="AK5" s="5" t="s">
-        <v>202</v>
+        <v>387</v>
       </c>
       <c r="AL5" s="5" t="s">
         <v>357</v>
@@ -13304,55 +13278,55 @@
         <v>87</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="C6" s="3">
-        <v>46219</v>
+        <v>46242</v>
       </c>
       <c r="D6" s="4">
-        <v>563202144</v>
+        <v>561246589</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="F6" s="6">
-        <v>46169</v>
+        <v>46163</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="K6" s="3">
-        <v>46250</v>
+        <v>46245</v>
       </c>
       <c r="L6" s="12">
         <f ca="1">IF($O6="","",$O6-TODAY())</f>
-        <v>-44</v>
+        <v>-50</v>
       </c>
       <c r="M6" s="12">
         <f ca="1">IF($C6="","",$C6+180-TODAY())</f>
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="N6" s="12">
         <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
-        <v>281</v>
+        <v>304</v>
       </c>
       <c r="O6" s="6">
-        <v>46259</v>
+        <v>46253</v>
       </c>
       <c r="P6" s="5" t="s">
         <v>46</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="R6" s="5" t="s">
         <v>48</v>
@@ -13366,14 +13340,16 @@
       <c r="U6" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="V6" s="5"/>
+      <c r="V6" s="5" t="s">
+        <v>319</v>
+      </c>
       <c r="W6" s="5"/>
       <c r="X6" s="5"/>
       <c r="Y6" s="5" t="s">
         <v>51</v>
       </c>
       <c r="Z6" s="7">
-        <v>11163.74</v>
+        <v>6297.27</v>
       </c>
       <c r="AA6" s="7">
         <v>0</v>
@@ -13382,29 +13358,27 @@
         <v>0</v>
       </c>
       <c r="AC6" s="6">
-        <v>46219</v>
+        <v>46183</v>
       </c>
       <c r="AD6" s="7">
-        <v>11163.74</v>
+        <v>6297.27</v>
       </c>
       <c r="AE6" s="4">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="AF6" s="5" t="s">
-        <v>201</v>
+        <v>394</v>
       </c>
       <c r="AG6" s="5" t="s">
-        <v>403</v>
+        <v>282</v>
       </c>
       <c r="AH6" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="AI6" s="5" t="s">
-        <v>405</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="AI6" s="5"/>
       <c r="AJ6" s="4"/>
       <c r="AK6" s="5" t="s">
-        <v>140</v>
+        <v>202</v>
       </c>
       <c r="AL6" s="5" t="s">
         <v>357</v>
@@ -13421,55 +13395,55 @@
         <v>87</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C7" s="3">
-        <v>46189</v>
+        <v>46219</v>
       </c>
       <c r="D7" s="4">
-        <v>561591684</v>
+        <v>563202144</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="F7" s="6">
-        <v>46143</v>
+        <v>46169</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>408</v>
+        <v>43</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>408</v>
+        <v>43</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="K7" s="3">
         <v>46250</v>
       </c>
       <c r="L7" s="12">
         <f ca="1">IF($O7="","",$O7-TODAY())</f>
-        <v>-40</v>
+        <v>-44</v>
       </c>
       <c r="M7" s="12">
         <f ca="1">IF($C7="","",$C7+180-TODAY())</f>
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="N7" s="12">
-        <f ca="1">IF($C7="","",$C7+180-TODAY())</f>
-        <v>66</v>
+        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
+        <v>281</v>
       </c>
       <c r="O7" s="6">
-        <v>46263</v>
+        <v>46259</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>108</v>
+        <v>47</v>
       </c>
       <c r="R7" s="5" t="s">
         <v>48</v>
@@ -13478,21 +13452,19 @@
         <v>49</v>
       </c>
       <c r="T7" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="U7" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="V7" s="5" t="s">
-        <v>302</v>
-      </c>
+      <c r="V7" s="5"/>
       <c r="W7" s="5"/>
       <c r="X7" s="5"/>
       <c r="Y7" s="5" t="s">
         <v>51</v>
       </c>
       <c r="Z7" s="7">
-        <v>5614.63</v>
+        <v>11163.74</v>
       </c>
       <c r="AA7" s="7">
         <v>0</v>
@@ -13501,29 +13473,35 @@
         <v>0</v>
       </c>
       <c r="AC7" s="6">
-        <v>46189</v>
+        <v>46219</v>
       </c>
       <c r="AD7" s="7">
-        <v>5614.63</v>
+        <v>11163.74</v>
       </c>
       <c r="AE7" s="4">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="AF7" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="AG7" s="5"/>
-      <c r="AH7" s="5"/>
-      <c r="AI7" s="5"/>
+        <v>201</v>
+      </c>
+      <c r="AG7" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="AH7" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="AI7" s="5" t="s">
+        <v>405</v>
+      </c>
       <c r="AJ7" s="4"/>
       <c r="AK7" s="5" t="s">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="AL7" s="5" t="s">
-        <v>54</v>
+        <v>357</v>
       </c>
       <c r="AM7" s="6">
-        <v>46181</v>
+        <v>46177</v>
       </c>
       <c r="AN7" s="5" t="s">
         <v>382</v>
@@ -13531,79 +13509,81 @@
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>220</v>
+        <v>406</v>
       </c>
       <c r="C8" s="3">
-        <v>46184</v>
+        <v>46189</v>
       </c>
       <c r="D8" s="4">
-        <v>568765283</v>
+        <v>561591684</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>221</v>
+        <v>407</v>
       </c>
       <c r="F8" s="6">
-        <v>46156</v>
+        <v>46143</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>222</v>
+        <v>408</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>222</v>
+        <v>408</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="K8" s="3">
         <v>46250</v>
       </c>
       <c r="L8" s="12">
         <f ca="1">IF($O8="","",$O8-TODAY())</f>
-        <v>-27</v>
+        <v>-40</v>
       </c>
       <c r="M8" s="12">
-        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
-        <v>246</v>
+        <f ca="1">IF($C8="","",$C8+180-TODAY())</f>
+        <v>66</v>
       </c>
       <c r="N8" s="12">
-        <f ca="1">IF($C8="","",$C8+90-TODAY())</f>
-        <v>-29</v>
+        <f ca="1">IF($C8="","",$C8+180-TODAY())</f>
+        <v>66</v>
       </c>
       <c r="O8" s="6">
-        <v>46276</v>
+        <v>46263</v>
       </c>
       <c r="P8" s="5" t="s">
         <v>103</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>224</v>
+        <v>108</v>
       </c>
       <c r="R8" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S8" s="5" t="s">
         <v>49</v>
       </c>
       <c r="T8" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="U8" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="V8" s="5"/>
+      <c r="V8" s="5" t="s">
+        <v>302</v>
+      </c>
       <c r="W8" s="5"/>
       <c r="X8" s="5"/>
       <c r="Y8" s="5" t="s">
         <v>51</v>
       </c>
       <c r="Z8" s="7">
-        <v>8277.57</v>
+        <v>5614.63</v>
       </c>
       <c r="AA8" s="7">
         <v>0</v>
@@ -13612,31 +13592,29 @@
         <v>0</v>
       </c>
       <c r="AC8" s="6">
-        <v>46184</v>
+        <v>46189</v>
       </c>
       <c r="AD8" s="7">
-        <v>8277.57</v>
+        <v>5614.63</v>
       </c>
       <c r="AE8" s="4">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="AF8" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="AG8" s="5" t="s">
-        <v>416</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="AG8" s="5"/>
       <c r="AH8" s="5"/>
       <c r="AI8" s="5"/>
       <c r="AJ8" s="4"/>
       <c r="AK8" s="5" t="s">
-        <v>202</v>
+        <v>85</v>
       </c>
       <c r="AL8" s="5" t="s">
-        <v>357</v>
+        <v>54</v>
       </c>
       <c r="AM8" s="6">
-        <v>46161</v>
+        <v>46181</v>
       </c>
       <c r="AN8" s="5" t="s">
         <v>382</v>
@@ -13644,58 +13622,58 @@
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>420</v>
+        <v>220</v>
       </c>
       <c r="C9" s="3">
-        <v>46157</v>
+        <v>46184</v>
       </c>
       <c r="D9" s="4">
-        <v>558809263</v>
+        <v>568765283</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>421</v>
+        <v>221</v>
       </c>
       <c r="F9" s="6">
-        <v>46143</v>
+        <v>46156</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>118</v>
+        <v>222</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>118</v>
+        <v>222</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="K9" s="3">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="L9" s="12">
         <f ca="1">IF($O9="","",$O9-TODAY())</f>
-        <v>205</v>
+        <v>-27</v>
       </c>
       <c r="M9" s="12">
         <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
-        <v>219</v>
+        <v>246</v>
       </c>
       <c r="N9" s="12">
-        <f ca="1">IF($C9="","",$C9+120-TODAY())</f>
-        <v>-26</v>
+        <f ca="1">IF($C9="","",$C9+90-TODAY())</f>
+        <v>-29</v>
       </c>
       <c r="O9" s="6">
-        <v>46508</v>
+        <v>46276</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>121</v>
+        <v>224</v>
       </c>
       <c r="R9" s="5" t="s">
         <v>50</v>
@@ -13704,21 +13682,19 @@
         <v>49</v>
       </c>
       <c r="T9" s="5" t="s">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="U9" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="V9" s="5" t="s">
-        <v>302</v>
-      </c>
+      <c r="V9" s="5"/>
       <c r="W9" s="5"/>
       <c r="X9" s="5"/>
       <c r="Y9" s="5" t="s">
         <v>51</v>
       </c>
       <c r="Z9" s="7">
-        <v>7623.07</v>
+        <v>8277.57</v>
       </c>
       <c r="AA9" s="7">
         <v>0</v>
@@ -13727,29 +13703,31 @@
         <v>0</v>
       </c>
       <c r="AC9" s="6">
-        <v>46157</v>
+        <v>46184</v>
       </c>
       <c r="AD9" s="7">
-        <v>7623.07</v>
+        <v>8277.57</v>
       </c>
       <c r="AE9" s="4">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="AF9" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="AG9" s="5"/>
+        <v>225</v>
+      </c>
+      <c r="AG9" s="5" t="s">
+        <v>416</v>
+      </c>
       <c r="AH9" s="5"/>
       <c r="AI9" s="5"/>
       <c r="AJ9" s="4"/>
       <c r="AK9" s="5" t="s">
-        <v>85</v>
+        <v>202</v>
       </c>
       <c r="AL9" s="5" t="s">
         <v>357</v>
       </c>
       <c r="AM9" s="6">
-        <v>46155</v>
+        <v>46161</v>
       </c>
       <c r="AN9" s="5" t="s">
         <v>382</v>
@@ -13760,19 +13738,19 @@
         <v>87</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C10" s="3">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="D10" s="4">
-        <v>569308141</v>
+        <v>558809263</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>266</v>
+        <v>421</v>
       </c>
       <c r="F10" s="6">
-        <v>46146</v>
+        <v>46143</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>118</v>
@@ -13781,28 +13759,28 @@
         <v>118</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>390</v>
+        <v>422</v>
       </c>
       <c r="K10" s="3">
-        <v>46254</v>
+        <v>46246</v>
       </c>
       <c r="L10" s="12">
         <f ca="1">IF($O10="","",$O10-TODAY())</f>
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="M10" s="12">
         <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="N10" s="12">
         <f ca="1">IF($C10="","",$C10+120-TODAY())</f>
-        <v>-22</v>
+        <v>-26</v>
       </c>
       <c r="O10" s="6">
-        <v>46511</v>
+        <v>46508</v>
       </c>
       <c r="P10" s="5" t="s">
         <v>50</v>
@@ -13822,14 +13800,16 @@
       <c r="U10" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="V10" s="5"/>
+      <c r="V10" s="5" t="s">
+        <v>302</v>
+      </c>
       <c r="W10" s="5"/>
       <c r="X10" s="5"/>
       <c r="Y10" s="5" t="s">
         <v>51</v>
       </c>
       <c r="Z10" s="7">
-        <v>2493.33</v>
+        <v>7623.07</v>
       </c>
       <c r="AA10" s="7">
         <v>0</v>
@@ -13838,32 +13818,26 @@
         <v>0</v>
       </c>
       <c r="AC10" s="6">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="AD10" s="7">
-        <v>2493.33</v>
+        <v>7623.07</v>
       </c>
       <c r="AE10" s="4">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="AF10" s="5" t="s">
-        <v>424</v>
-      </c>
-      <c r="AG10" s="5" t="s">
-        <v>425</v>
-      </c>
-      <c r="AH10" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="AI10" s="5" t="s">
-        <v>267</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="AG10" s="5"/>
+      <c r="AH10" s="5"/>
+      <c r="AI10" s="5"/>
       <c r="AJ10" s="4"/>
       <c r="AK10" s="5" t="s">
-        <v>207</v>
+        <v>85</v>
       </c>
       <c r="AL10" s="5" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="AM10" s="6">
         <v>46155</v>
@@ -13877,19 +13851,19 @@
         <v>87</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C11" s="3">
-        <v>46245</v>
+        <v>46161</v>
       </c>
       <c r="D11" s="4">
-        <v>559152944</v>
+        <v>569308141</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="F11" s="6">
-        <v>46153</v>
+        <v>46146</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>118</v>
@@ -13898,28 +13872,28 @@
         <v>118</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>272</v>
+        <v>131</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>427</v>
+        <v>390</v>
       </c>
       <c r="K11" s="3">
-        <v>46259</v>
+        <v>46254</v>
       </c>
       <c r="L11" s="12">
         <f ca="1">IF($O11="","",$O11-TODAY())</f>
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="M11" s="12">
         <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
-        <v>307</v>
+        <v>223</v>
       </c>
       <c r="N11" s="12">
         <f ca="1">IF($C11="","",$C11+120-TODAY())</f>
-        <v>62</v>
+        <v>-22</v>
       </c>
       <c r="O11" s="6">
-        <v>46518</v>
+        <v>46511</v>
       </c>
       <c r="P11" s="5" t="s">
         <v>50</v>
@@ -13946,7 +13920,7 @@
         <v>51</v>
       </c>
       <c r="Z11" s="7">
-        <v>5784.24</v>
+        <v>2493.33</v>
       </c>
       <c r="AA11" s="7">
         <v>0</v>
@@ -13955,29 +13929,35 @@
         <v>0</v>
       </c>
       <c r="AC11" s="6">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="AD11" s="7">
-        <v>5784.24</v>
+        <v>2493.33</v>
       </c>
       <c r="AE11" s="4">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="AF11" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="AG11" s="5"/>
-      <c r="AH11" s="5"/>
-      <c r="AI11" s="5"/>
+        <v>424</v>
+      </c>
+      <c r="AG11" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="AH11" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="AI11" s="5" t="s">
+        <v>267</v>
+      </c>
       <c r="AJ11" s="4"/>
       <c r="AK11" s="5" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="AL11" s="5" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="AM11" s="6">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="AN11" s="5" t="s">
         <v>382</v>
@@ -13988,19 +13968,19 @@
         <v>87</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C12" s="3">
-        <v>46168</v>
+        <v>46245</v>
       </c>
       <c r="D12" s="4">
-        <v>559435670</v>
+        <v>559152944</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>429</v>
+        <v>271</v>
       </c>
       <c r="F12" s="6">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>118</v>
@@ -14009,28 +13989,28 @@
         <v>118</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>44</v>
+        <v>272</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="K12" s="3">
         <v>46259</v>
       </c>
       <c r="L12" s="12">
         <f ca="1">IF($O12="","",$O12-TODAY())</f>
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="M12" s="12">
         <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
-        <v>230</v>
+        <v>307</v>
       </c>
       <c r="N12" s="12">
         <f ca="1">IF($C12="","",$C12+120-TODAY())</f>
-        <v>-15</v>
+        <v>62</v>
       </c>
       <c r="O12" s="6">
-        <v>46520</v>
+        <v>46518</v>
       </c>
       <c r="P12" s="5" t="s">
         <v>50</v>
@@ -14050,16 +14030,14 @@
       <c r="U12" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="V12" s="5" t="s">
-        <v>319</v>
-      </c>
+      <c r="V12" s="5"/>
       <c r="W12" s="5"/>
       <c r="X12" s="5"/>
       <c r="Y12" s="5" t="s">
         <v>51</v>
       </c>
       <c r="Z12" s="7">
-        <v>5614.63</v>
+        <v>5784.24</v>
       </c>
       <c r="AA12" s="7">
         <v>0</v>
@@ -14068,29 +14046,29 @@
         <v>0</v>
       </c>
       <c r="AC12" s="6">
-        <v>46168</v>
+        <v>46160</v>
       </c>
       <c r="AD12" s="7">
-        <v>5614.63</v>
+        <v>5784.24</v>
       </c>
       <c r="AE12" s="4">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AF12" s="5" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="AG12" s="5"/>
       <c r="AH12" s="5"/>
       <c r="AI12" s="5"/>
       <c r="AJ12" s="4"/>
       <c r="AK12" s="5" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="AL12" s="5" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="AM12" s="6">
-        <v>46160</v>
+        <v>46156</v>
       </c>
       <c r="AN12" s="5" t="s">
         <v>382</v>
@@ -14101,19 +14079,19 @@
         <v>87</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="C13" s="3">
         <v>46168</v>
       </c>
       <c r="D13" s="4">
-        <v>559339992</v>
+        <v>559435670</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F13" s="6">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>118</v>
@@ -14122,17 +14100,17 @@
         <v>118</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>272</v>
+        <v>44</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>390</v>
+        <v>430</v>
       </c>
       <c r="K13" s="3">
         <v>46259</v>
       </c>
       <c r="L13" s="12">
         <f ca="1">IF($O13="","",$O13-TODAY())</f>
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="M13" s="12">
         <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
@@ -14143,7 +14121,7 @@
         <v>-15</v>
       </c>
       <c r="O13" s="6">
-        <v>46522</v>
+        <v>46520</v>
       </c>
       <c r="P13" s="5" t="s">
         <v>50</v>
@@ -14163,14 +14141,16 @@
       <c r="U13" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="V13" s="5"/>
+      <c r="V13" s="5" t="s">
+        <v>319</v>
+      </c>
       <c r="W13" s="5"/>
       <c r="X13" s="5"/>
       <c r="Y13" s="5" t="s">
         <v>51</v>
       </c>
       <c r="Z13" s="7">
-        <v>2493.33</v>
+        <v>5614.63</v>
       </c>
       <c r="AA13" s="7">
         <v>0</v>
@@ -14182,27 +14162,23 @@
         <v>46168</v>
       </c>
       <c r="AD13" s="7">
-        <v>2493.33</v>
+        <v>5614.63</v>
       </c>
       <c r="AE13" s="4">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AF13" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="AG13" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="AH13" s="5" t="s">
-        <v>174</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="AG13" s="5"/>
+      <c r="AH13" s="5"/>
       <c r="AI13" s="5"/>
       <c r="AJ13" s="4"/>
       <c r="AK13" s="5" t="s">
-        <v>76</v>
+        <v>207</v>
       </c>
       <c r="AL13" s="5" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="AM13" s="6">
         <v>46160</v>
@@ -14213,52 +14189,52 @@
     </row>
     <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="C14" s="3">
-        <v>46189</v>
+        <v>46168</v>
       </c>
       <c r="D14" s="4">
-        <v>560691343</v>
+        <v>559339992</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F14" s="6">
-        <v>46171</v>
+        <v>46157</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>118</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>43</v>
+        <v>272</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>390</v>
       </c>
       <c r="K14" s="3">
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="L14" s="12">
         <f ca="1">IF($O14="","",$O14-TODAY())</f>
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="M14" s="12">
         <f ca="1">IF($C14="","",$C14+365-TODAY())</f>
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="N14" s="12">
         <f ca="1">IF($C14="","",$C14+120-TODAY())</f>
-        <v>6</v>
+        <v>-15</v>
       </c>
       <c r="O14" s="6">
-        <v>46536</v>
+        <v>46522</v>
       </c>
       <c r="P14" s="5" t="s">
         <v>50</v>
@@ -14288,39 +14264,39 @@
         <v>2493.33</v>
       </c>
       <c r="AA14" s="7">
-        <v>2351.73</v>
+        <v>0</v>
       </c>
       <c r="AB14" s="7">
-        <v>110.6</v>
+        <v>0</v>
       </c>
       <c r="AC14" s="6">
-        <v>46189</v>
+        <v>46168</v>
       </c>
       <c r="AD14" s="7">
-        <v>31</v>
+        <v>2493.33</v>
       </c>
       <c r="AE14" s="4">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="AF14" s="5" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="AG14" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="AH14" s="5"/>
+        <v>211</v>
+      </c>
+      <c r="AH14" s="5" t="s">
+        <v>174</v>
+      </c>
       <c r="AI14" s="5"/>
-      <c r="AJ14" s="4">
-        <v>563761052</v>
-      </c>
+      <c r="AJ14" s="4"/>
       <c r="AK14" s="5" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="AL14" s="5" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="AM14" s="6">
-        <v>46175</v>
+        <v>46160</v>
       </c>
       <c r="AN14" s="5" t="s">
         <v>382</v>
@@ -14328,67 +14304,67 @@
     </row>
     <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C15" s="3">
-        <v>46170</v>
+        <v>46189</v>
       </c>
       <c r="D15" s="4">
-        <v>558165481</v>
+        <v>560691343</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F15" s="6">
-        <v>46146</v>
+        <v>46171</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>437</v>
+        <v>43</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>437</v>
+        <v>118</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="K15" s="3">
         <v>46256</v>
       </c>
       <c r="L15" s="12">
         <f ca="1">IF($O15="","",$O15-TODAY())</f>
-        <v>-67</v>
+        <v>233</v>
       </c>
       <c r="M15" s="12">
-        <f ca="1">IF($C15="","",$C15+180-TODAY())</f>
-        <v>47</v>
+        <f ca="1">IF($C15="","",$C15+365-TODAY())</f>
+        <v>251</v>
       </c>
       <c r="N15" s="12">
-        <f ca="1">IF($C15="","",$C15+365-TODAY())</f>
-        <v>232</v>
+        <f ca="1">IF($C15="","",$C15+120-TODAY())</f>
+        <v>6</v>
       </c>
       <c r="O15" s="6">
-        <v>46236</v>
+        <v>46536</v>
       </c>
       <c r="P15" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>438</v>
+        <v>121</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>49</v>
       </c>
       <c r="T15" s="5" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="U15" s="5" t="s">
         <v>49</v>
@@ -14400,38 +14376,42 @@
         <v>51</v>
       </c>
       <c r="Z15" s="7">
-        <v>7623.07</v>
+        <v>2493.33</v>
       </c>
       <c r="AA15" s="7">
-        <v>0</v>
+        <v>2351.73</v>
       </c>
       <c r="AB15" s="7">
-        <v>0</v>
+        <v>110.6</v>
       </c>
       <c r="AC15" s="6">
-        <v>46170</v>
+        <v>46189</v>
       </c>
       <c r="AD15" s="7">
-        <v>7623.07</v>
+        <v>31</v>
       </c>
       <c r="AE15" s="4">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="AF15" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="AG15" s="5"/>
+        <v>193</v>
+      </c>
+      <c r="AG15" s="5" t="s">
+        <v>434</v>
+      </c>
       <c r="AH15" s="5"/>
       <c r="AI15" s="5"/>
-      <c r="AJ15" s="4"/>
+      <c r="AJ15" s="4">
+        <v>563761052</v>
+      </c>
       <c r="AK15" s="5" t="s">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="AL15" s="5" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="AM15" s="6">
-        <v>46153</v>
+        <v>46175</v>
       </c>
       <c r="AN15" s="5" t="s">
         <v>382</v>
@@ -14439,64 +14419,64 @@
     </row>
     <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>530</v>
+        <v>87</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>537</v>
+        <v>435</v>
       </c>
       <c r="C16" s="3">
-        <v>46197</v>
+        <v>46170</v>
       </c>
       <c r="D16" s="4">
-        <v>558351506</v>
+        <v>558165481</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>336</v>
+        <v>436</v>
       </c>
       <c r="F16" s="6">
-        <v>46148</v>
+        <v>46146</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>131</v>
+        <v>437</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>131</v>
+        <v>437</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="K16" s="3">
-        <v>46177</v>
+        <v>46256</v>
       </c>
       <c r="L16" s="12">
         <f ca="1">IF($O16="","",$O16-TODAY())</f>
-        <v>-65</v>
+        <v>-67</v>
       </c>
       <c r="M16" s="12">
-        <f ca="1">IF($F16="","",$F16+90-TODAY())</f>
-        <v>-65</v>
+        <f ca="1">IF($C16="","",$C16+180-TODAY())</f>
+        <v>47</v>
       </c>
       <c r="N16" s="12">
         <f ca="1">IF($C16="","",$C16+365-TODAY())</f>
-        <v>259</v>
+        <v>232</v>
       </c>
       <c r="O16" s="6">
-        <v>46238</v>
+        <v>46236</v>
       </c>
       <c r="P16" s="5" t="s">
         <v>46</v>
       </c>
       <c r="Q16" s="5" t="s">
-        <v>152</v>
+        <v>438</v>
       </c>
       <c r="R16" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S16" s="5" t="s">
-        <v>191</v>
+        <v>49</v>
       </c>
       <c r="T16" s="5" t="s">
         <v>50</v>
@@ -14511,7 +14491,7 @@
         <v>51</v>
       </c>
       <c r="Z16" s="7">
-        <v>2493.33</v>
+        <v>7623.07</v>
       </c>
       <c r="AA16" s="7">
         <v>0</v>
@@ -14520,31 +14500,29 @@
         <v>0</v>
       </c>
       <c r="AC16" s="6">
-        <v>46197</v>
+        <v>46170</v>
       </c>
       <c r="AD16" s="7">
-        <v>2493.33</v>
+        <v>7623.07</v>
       </c>
       <c r="AE16" s="4">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AF16" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="AG16" s="5" t="s">
-        <v>282</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="AG16" s="5"/>
       <c r="AH16" s="5"/>
       <c r="AI16" s="5"/>
       <c r="AJ16" s="4"/>
       <c r="AK16" s="5" t="s">
-        <v>81</v>
+        <v>140</v>
       </c>
       <c r="AL16" s="5" t="s">
         <v>357</v>
       </c>
       <c r="AM16" s="6">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="AN16" s="5" t="s">
         <v>382</v>
@@ -14552,64 +14530,64 @@
     </row>
     <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>87</v>
+        <v>530</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>439</v>
+        <v>537</v>
       </c>
       <c r="C17" s="3">
-        <v>46262</v>
+        <v>46197</v>
       </c>
       <c r="D17" s="4">
-        <v>559605223</v>
+        <v>558351506</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>169</v>
+        <v>336</v>
       </c>
       <c r="F17" s="6">
-        <v>46155</v>
+        <v>46148</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>440</v>
+        <v>390</v>
       </c>
       <c r="K17" s="3">
-        <v>46244</v>
+        <v>46177</v>
       </c>
       <c r="L17" s="12">
         <f ca="1">IF($O17="","",$O17-TODAY())</f>
-        <v>-58</v>
+        <v>-65</v>
       </c>
       <c r="M17" s="12">
-        <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
-        <v>324</v>
+        <f ca="1">IF($F17="","",$F17+90-TODAY())</f>
+        <v>-65</v>
       </c>
       <c r="N17" s="12">
         <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
-        <v>324</v>
+        <v>259</v>
       </c>
       <c r="O17" s="6">
-        <v>46245</v>
+        <v>46238</v>
       </c>
       <c r="P17" s="5" t="s">
         <v>46</v>
       </c>
       <c r="Q17" s="5" t="s">
-        <v>96</v>
+        <v>152</v>
       </c>
       <c r="R17" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="S17" s="5" t="s">
-        <v>49</v>
+        <v>191</v>
       </c>
       <c r="T17" s="5" t="s">
         <v>50</v>
@@ -14617,16 +14595,14 @@
       <c r="U17" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="V17" s="5" t="s">
-        <v>344</v>
-      </c>
+      <c r="V17" s="5"/>
       <c r="W17" s="5"/>
       <c r="X17" s="5"/>
       <c r="Y17" s="5" t="s">
         <v>51</v>
       </c>
       <c r="Z17" s="7">
-        <v>20158.46</v>
+        <v>2493.33</v>
       </c>
       <c r="AA17" s="7">
         <v>0</v>
@@ -14634,34 +14610,32 @@
       <c r="AB17" s="7">
         <v>0</v>
       </c>
-      <c r="AC17" s="6"/>
+      <c r="AC17" s="6">
+        <v>46197</v>
+      </c>
       <c r="AD17" s="7">
-        <v>20158.46</v>
+        <v>2493.33</v>
       </c>
       <c r="AE17" s="4">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="AF17" s="5" t="s">
-        <v>441</v>
+        <v>225</v>
       </c>
       <c r="AG17" s="5" t="s">
-        <v>442</v>
-      </c>
-      <c r="AH17" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="AI17" s="5" t="s">
-        <v>444</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="AH17" s="5"/>
+      <c r="AI17" s="5"/>
       <c r="AJ17" s="4"/>
       <c r="AK17" s="5" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="AL17" s="5" t="s">
         <v>357</v>
       </c>
       <c r="AM17" s="6">
-        <v>46161</v>
+        <v>46149</v>
       </c>
       <c r="AN17" s="5" t="s">
         <v>382</v>
@@ -14669,79 +14643,81 @@
     </row>
     <row r="18" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>388</v>
+        <v>439</v>
       </c>
       <c r="C18" s="3">
-        <v>46170</v>
+        <v>46262</v>
       </c>
       <c r="D18" s="4">
-        <v>559340087</v>
+        <v>559605223</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>389</v>
+        <v>169</v>
       </c>
       <c r="F18" s="6">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>390</v>
+        <v>440</v>
       </c>
       <c r="K18" s="3">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="L18" s="12">
         <f ca="1">IF($O18="","",$O18-TODAY())</f>
-        <v>-51</v>
+        <v>-58</v>
       </c>
       <c r="M18" s="12">
-        <f ca="1">IF($C18="","",$C18+90-TODAY())</f>
-        <v>-43</v>
+        <f ca="1">IF($C18="","",$C18+365-TODAY())</f>
+        <v>324</v>
       </c>
       <c r="N18" s="12">
-        <f ca="1">IF($C18="","",$C18+90-TODAY())</f>
-        <v>-43</v>
+        <f ca="1">IF($C18="","",$C18+365-TODAY())</f>
+        <v>324</v>
       </c>
       <c r="O18" s="6">
-        <v>46252</v>
+        <v>46245</v>
       </c>
       <c r="P18" s="5" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="Q18" s="5" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="R18" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="S18" s="5" t="s">
         <v>49</v>
       </c>
       <c r="T18" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="U18" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="V18" s="5"/>
+      <c r="V18" s="5" t="s">
+        <v>344</v>
+      </c>
       <c r="W18" s="5"/>
       <c r="X18" s="5"/>
       <c r="Y18" s="5" t="s">
         <v>51</v>
       </c>
       <c r="Z18" s="7">
-        <v>2493.33</v>
+        <v>20158.46</v>
       </c>
       <c r="AA18" s="7">
         <v>0</v>
@@ -14749,34 +14725,34 @@
       <c r="AB18" s="7">
         <v>0</v>
       </c>
-      <c r="AC18" s="6">
-        <v>46170</v>
-      </c>
+      <c r="AC18" s="6"/>
       <c r="AD18" s="7">
-        <v>2493.33</v>
+        <v>20158.46</v>
       </c>
       <c r="AE18" s="4">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AF18" s="5" t="s">
-        <v>225</v>
+        <v>441</v>
       </c>
       <c r="AG18" s="5" t="s">
-        <v>211</v>
+        <v>442</v>
       </c>
       <c r="AH18" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="AI18" s="5"/>
+        <v>443</v>
+      </c>
+      <c r="AI18" s="5" t="s">
+        <v>444</v>
+      </c>
       <c r="AJ18" s="4"/>
       <c r="AK18" s="5" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="AL18" s="5" t="s">
         <v>357</v>
       </c>
       <c r="AM18" s="6">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="AN18" s="5" t="s">
         <v>382</v>
@@ -14787,25 +14763,25 @@
         <v>115</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="C19" s="3">
-        <v>46231</v>
+        <v>46170</v>
       </c>
       <c r="D19" s="4">
-        <v>565698268</v>
+        <v>559340087</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="F19" s="6">
-        <v>46168</v>
+        <v>46157</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>323</v>
+        <v>62</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>323</v>
+        <v>62</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>44</v>
@@ -14818,33 +14794,33 @@
       </c>
       <c r="L19" s="12">
         <f ca="1">IF($O19="","",$O19-TODAY())</f>
-        <v>-45</v>
+        <v>-51</v>
       </c>
       <c r="M19" s="12">
-        <f ca="1">IF($F19="","",$F19+90-TODAY())</f>
-        <v>-45</v>
+        <f ca="1">IF($C19="","",$C19+90-TODAY())</f>
+        <v>-43</v>
       </c>
       <c r="N19" s="12">
-        <f ca="1">IF($C19="","",$C19+180-TODAY())</f>
-        <v>108</v>
+        <f ca="1">IF($C19="","",$C19+90-TODAY())</f>
+        <v>-43</v>
       </c>
       <c r="O19" s="6">
-        <v>46258</v>
+        <v>46252</v>
       </c>
       <c r="P19" s="5" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="Q19" s="5" t="s">
-        <v>325</v>
+        <v>66</v>
       </c>
       <c r="R19" s="5" t="s">
         <v>46</v>
       </c>
       <c r="S19" s="5" t="s">
-        <v>191</v>
+        <v>49</v>
       </c>
       <c r="T19" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="U19" s="5" t="s">
         <v>49</v>
@@ -14864,30 +14840,34 @@
       <c r="AB19" s="7">
         <v>0</v>
       </c>
-      <c r="AC19" s="6"/>
+      <c r="AC19" s="6">
+        <v>46170</v>
+      </c>
       <c r="AD19" s="7">
         <v>2493.33</v>
       </c>
       <c r="AE19" s="4">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="AF19" s="5" t="s">
-        <v>398</v>
+        <v>225</v>
       </c>
       <c r="AG19" s="5" t="s">
-        <v>399</v>
-      </c>
-      <c r="AH19" s="5"/>
+        <v>211</v>
+      </c>
+      <c r="AH19" s="5" t="s">
+        <v>174</v>
+      </c>
       <c r="AI19" s="5"/>
       <c r="AJ19" s="4"/>
       <c r="AK19" s="5" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="AL19" s="5" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="AM19" s="6">
-        <v>46170</v>
+        <v>46160</v>
       </c>
       <c r="AN19" s="5" t="s">
         <v>382</v>
@@ -14898,61 +14878,61 @@
         <v>115</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>410</v>
+        <v>396</v>
       </c>
       <c r="C20" s="3">
-        <v>46164</v>
+        <v>46231</v>
       </c>
       <c r="D20" s="4">
-        <v>559152456</v>
+        <v>565698268</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="F20" s="6">
-        <v>46153</v>
+        <v>46168</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>408</v>
+        <v>323</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>408</v>
+        <v>323</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>412</v>
+        <v>390</v>
       </c>
       <c r="K20" s="3">
-        <v>46250</v>
+        <v>46245</v>
       </c>
       <c r="L20" s="12">
         <f ca="1">IF($O20="","",$O20-TODAY())</f>
-        <v>-30</v>
+        <v>-45</v>
       </c>
       <c r="M20" s="12">
-        <f ca="1">IF($C20="","",$C20+180-TODAY())</f>
-        <v>41</v>
+        <f ca="1">IF($F20="","",$F20+90-TODAY())</f>
+        <v>-45</v>
       </c>
       <c r="N20" s="12">
         <f ca="1">IF($C20="","",$C20+180-TODAY())</f>
-        <v>41</v>
+        <v>108</v>
       </c>
       <c r="O20" s="6">
-        <v>46273</v>
+        <v>46258</v>
       </c>
       <c r="P20" s="5" t="s">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="Q20" s="5" t="s">
-        <v>108</v>
+        <v>325</v>
       </c>
       <c r="R20" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S20" s="5" t="s">
-        <v>49</v>
+        <v>191</v>
       </c>
       <c r="T20" s="5" t="s">
         <v>48</v>
@@ -14960,16 +14940,14 @@
       <c r="U20" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="V20" s="5" t="s">
-        <v>413</v>
-      </c>
+      <c r="V20" s="5"/>
       <c r="W20" s="5"/>
       <c r="X20" s="5"/>
       <c r="Y20" s="5" t="s">
         <v>51</v>
       </c>
       <c r="Z20" s="7">
-        <v>13920.34</v>
+        <v>2493.33</v>
       </c>
       <c r="AA20" s="7">
         <v>0</v>
@@ -14977,36 +14955,30 @@
       <c r="AB20" s="7">
         <v>0</v>
       </c>
-      <c r="AC20" s="6">
-        <v>46164</v>
-      </c>
+      <c r="AC20" s="6"/>
       <c r="AD20" s="7">
-        <v>13920.34</v>
+        <v>2493.33</v>
       </c>
       <c r="AE20" s="4">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="AF20" s="5" t="s">
-        <v>288</v>
+        <v>398</v>
       </c>
       <c r="AG20" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="AH20" s="5" t="s">
-        <v>414</v>
-      </c>
-      <c r="AI20" s="5" t="s">
-        <v>287</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="AH20" s="5"/>
+      <c r="AI20" s="5"/>
       <c r="AJ20" s="4"/>
       <c r="AK20" s="5" t="s">
-        <v>202</v>
+        <v>97</v>
       </c>
       <c r="AL20" s="5" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="AM20" s="6">
-        <v>46156</v>
+        <v>46170</v>
       </c>
       <c r="AN20" s="5" t="s">
         <v>382</v>
@@ -15017,19 +14989,19 @@
         <v>115</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="C21" s="3">
-        <v>46171</v>
+        <v>46164</v>
       </c>
       <c r="D21" s="4">
-        <v>559655054</v>
+        <v>559152456</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="F21" s="6">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>408</v>
@@ -15041,25 +15013,25 @@
         <v>44</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>381</v>
+        <v>412</v>
       </c>
       <c r="K21" s="3">
         <v>46250</v>
       </c>
       <c r="L21" s="12">
         <f ca="1">IF($O21="","",$O21-TODAY())</f>
-        <v>-27</v>
+        <v>-30</v>
       </c>
       <c r="M21" s="12">
         <f ca="1">IF($C21="","",$C21+180-TODAY())</f>
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="N21" s="12">
         <f ca="1">IF($C21="","",$C21+180-TODAY())</f>
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="O21" s="6">
-        <v>46276</v>
+        <v>46273</v>
       </c>
       <c r="P21" s="5" t="s">
         <v>103</v>
@@ -15079,14 +15051,16 @@
       <c r="U21" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="V21" s="5"/>
+      <c r="V21" s="5" t="s">
+        <v>413</v>
+      </c>
       <c r="W21" s="5"/>
       <c r="X21" s="5"/>
       <c r="Y21" s="5" t="s">
         <v>51</v>
       </c>
       <c r="Z21" s="7">
-        <v>7623.07</v>
+        <v>13920.34</v>
       </c>
       <c r="AA21" s="7">
         <v>0</v>
@@ -15094,12 +15068,14 @@
       <c r="AB21" s="7">
         <v>0</v>
       </c>
-      <c r="AC21" s="6"/>
+      <c r="AC21" s="6">
+        <v>46164</v>
+      </c>
       <c r="AD21" s="7">
-        <v>7623.07</v>
+        <v>13920.34</v>
       </c>
       <c r="AE21" s="4">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AF21" s="5" t="s">
         <v>288</v>
@@ -15107,8 +15083,12 @@
       <c r="AG21" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="AH21" s="5"/>
-      <c r="AI21" s="5"/>
+      <c r="AH21" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="AI21" s="5" t="s">
+        <v>287</v>
+      </c>
       <c r="AJ21" s="4"/>
       <c r="AK21" s="5" t="s">
         <v>202</v>
@@ -15117,7 +15097,7 @@
         <v>357</v>
       </c>
       <c r="AM21" s="6">
-        <v>46161</v>
+        <v>46156</v>
       </c>
       <c r="AN21" s="5" t="s">
         <v>382</v>
@@ -15128,61 +15108,61 @@
         <v>115</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C22" s="3">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="D22" s="4">
-        <v>559248529</v>
+        <v>559655054</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>236</v>
+        <v>418</v>
       </c>
       <c r="F22" s="6">
         <v>46156</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>237</v>
+        <v>408</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>237</v>
+        <v>408</v>
       </c>
       <c r="I22" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="K22" s="3">
-        <v>46252</v>
+        <v>46250</v>
       </c>
       <c r="L22" s="12">
         <f ca="1">IF($O22="","",$O22-TODAY())</f>
-        <v>33</v>
+        <v>-27</v>
       </c>
       <c r="M22" s="12">
-        <f ca="1">IF($F22="","",$F22+180-TODAY())</f>
-        <v>33</v>
+        <f ca="1">IF($C22="","",$C22+180-TODAY())</f>
+        <v>48</v>
       </c>
       <c r="N22" s="12">
         <f ca="1">IF($C22="","",$C22+180-TODAY())</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O22" s="6">
-        <v>46336</v>
+        <v>46276</v>
       </c>
       <c r="P22" s="5" t="s">
-        <v>48</v>
+        <v>103</v>
       </c>
       <c r="Q22" s="5" t="s">
-        <v>238</v>
+        <v>108</v>
       </c>
       <c r="R22" s="5" t="s">
         <v>48</v>
       </c>
       <c r="S22" s="5" t="s">
-        <v>191</v>
+        <v>49</v>
       </c>
       <c r="T22" s="5" t="s">
         <v>48</v>
@@ -15197,7 +15177,7 @@
         <v>51</v>
       </c>
       <c r="Z22" s="7">
-        <v>2493.33</v>
+        <v>7623.07</v>
       </c>
       <c r="AA22" s="7">
         <v>0</v>
@@ -15205,30 +15185,30 @@
       <c r="AB22" s="7">
         <v>0</v>
       </c>
-      <c r="AC22" s="6">
-        <v>46170</v>
-      </c>
+      <c r="AC22" s="6"/>
       <c r="AD22" s="7">
-        <v>2493.33</v>
+        <v>7623.07</v>
       </c>
       <c r="AE22" s="4">
         <v>86</v>
       </c>
       <c r="AF22" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="AG22" s="5"/>
+        <v>288</v>
+      </c>
+      <c r="AG22" s="5" t="s">
+        <v>211</v>
+      </c>
       <c r="AH22" s="5"/>
       <c r="AI22" s="5"/>
       <c r="AJ22" s="4"/>
       <c r="AK22" s="5" t="s">
-        <v>97</v>
+        <v>202</v>
       </c>
       <c r="AL22" s="5" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="AM22" s="6">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="AN22" s="5" t="s">
         <v>382</v>
@@ -15236,61 +15216,79 @@
     </row>
     <row r="23" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>445</v>
+        <v>419</v>
       </c>
       <c r="C23" s="3">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="D23" s="4">
-        <v>558845008</v>
+        <v>559248529</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>339</v>
+        <v>236</v>
       </c>
       <c r="F23" s="6">
-        <v>46146</v>
+        <v>46156</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>155</v>
+        <v>237</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>155</v>
+        <v>237</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="K23" s="3"/>
-      <c r="L23" s="12" t="str">
+        <v>390</v>
+      </c>
+      <c r="K23" s="3">
+        <v>46252</v>
+      </c>
+      <c r="L23" s="12">
         <f ca="1">IF($O23="","",$O23-TODAY())</f>
-        <v/>
-      </c>
-      <c r="M23" s="12"/>
-      <c r="N23" s="12"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="M23" s="12">
+        <f ca="1">IF($F23="","",$F23+180-TODAY())</f>
+        <v>33</v>
+      </c>
+      <c r="N23" s="12">
+        <f ca="1">IF($C23="","",$C23+180-TODAY())</f>
+        <v>47</v>
+      </c>
+      <c r="O23" s="6">
+        <v>46336</v>
+      </c>
+      <c r="P23" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="Q23" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="R23" s="5"/>
-      <c r="S23" s="5"/>
-      <c r="T23" s="5"/>
-      <c r="U23" s="5"/>
-      <c r="V23" s="5" t="s">
-        <v>319</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="R23" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="S23" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="T23" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="U23" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="V23" s="5"/>
       <c r="W23" s="5"/>
       <c r="X23" s="5"/>
       <c r="Y23" s="5" t="s">
         <v>51</v>
       </c>
       <c r="Z23" s="7">
-        <v>5614.63</v>
+        <v>2493.33</v>
       </c>
       <c r="AA23" s="7">
         <v>0</v>
@@ -15298,28 +15296,30 @@
       <c r="AB23" s="7">
         <v>0</v>
       </c>
-      <c r="AC23" s="6"/>
+      <c r="AC23" s="6">
+        <v>46170</v>
+      </c>
       <c r="AD23" s="7">
-        <v>5614.63</v>
+        <v>2493.33</v>
       </c>
       <c r="AE23" s="4">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="AF23" s="5" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="AG23" s="5"/>
       <c r="AH23" s="5"/>
       <c r="AI23" s="5"/>
       <c r="AJ23" s="4"/>
       <c r="AK23" s="5" t="s">
-        <v>207</v>
+        <v>97</v>
       </c>
       <c r="AL23" s="5" t="s">
         <v>349</v>
       </c>
       <c r="AM23" s="6">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="AN23" s="5" t="s">
         <v>382</v>

--- a/SPC26S1 - 05 May.xlsx
+++ b/SPC26S1 - 05 May.xlsx
@@ -2531,7 +2531,7 @@
     <t>Past due rows sit below the claims that can still be filed on time rather than at the very top, so the actionable work stays first. That is why the numbers run up to the longest window and then restart at the negatives.</t>
   </si>
   <si>
-    <t>Filing Deadline is the date of service plus the primary payer's limit, taken from 'Carrier_Timely_Filing_Reference.xlsx'. Days Until Deadline is a live formula, so the count stays true as time passes - but the row order is a snapshot taken on 12 August 2026. Sorting on Days Until Deadline alone would mix the three groups above back together, so when you re-sort keep the empty Latest Date Worked rows first and the Finalized and PAID rows last.</t>
+    <t>Filing Deadline is the date of service plus the primary payer's limit, taken from 'Carrier_Timely_Filing_Reference.xlsx'. Days Until Deadline is a live formula, so the count stays true as time passes - but the row order is a snapshot taken on 12 August 2026. Sorting on Days Until Deadline alone would mix the four groups above back together, so when you re-sort keep the Rejected rows first, then the empty Latest Date Worked rows, and the Finalized and PAID rows last.</t>
   </si>
   <si>
     <t>Where a payer had two possible limits the shorter one was used, so the real deadline can only be later, never earlier. Filing Limit and Limit Carrier name the figure applied and the carrier row it came from.</t>
@@ -2633,7 +2633,7 @@
     <t>107 claims with a date of service in 2026-05 May, split into one sheet per specialty: BH, DME, GAE, ORTHO, US.</t>
   </si>
   <si>
-    <t>Every specialty sheet is sorted in three groups: claims with an empty Latest Date Worked (column K) at the top, then the other open claims, and Finalized and PAID claims at the bottom (a Finalized or PAID claim with an empty Latest Date Worked stays in the top group). Within each group, rows are ordered by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: five days or less left is shaded red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
+    <t>Every specialty sheet is sorted in four groups: Rejected claims at the very top, then claims with an empty Latest Date Worked (column K), then the other open claims, and Finalized and PAID claims at the bottom (a Finalized or PAID claim with an empty Latest Date Worked stays in the empty Latest Date Worked group). Within each group, rows are ordered by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: five days or less left is shaded red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
   </si>
   <si>
     <t>Deadline order within each group, with the colour band each row gets, counted on 19 September 2026:</t>
@@ -4303,56 +4303,56 @@
     </row>
     <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>530</v>
+        <v>98</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="C2" s="3">
-        <v>46195</v>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="C2" s="3"/>
       <c r="D2" s="4">
-        <v>560450629</v>
+        <v>558010066</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F2" s="6">
-        <v>46169</v>
+        <v>46143</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="K2" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="K2" s="3">
+        <v>46300</v>
+      </c>
       <c r="L2" s="12">
         <f ca="1">IF($O2="","",$O2-TODAY())</f>
-        <v>-14</v>
-      </c>
-      <c r="M2" s="12">
+        <v>-70</v>
+      </c>
+      <c r="M2" s="12" t="str">
         <f ca="1">IF($C2="","",$C2+180-TODAY())</f>
-        <v>72</v>
-      </c>
-      <c r="N2" s="12">
-        <f ca="1">IF($C2="","",$C2+180-TODAY())</f>
-        <v>72</v>
+        <v/>
+      </c>
+      <c r="N2" s="12" t="str">
+        <f ca="1">IF($C2="","",$C2+365-TODAY())</f>
+        <v/>
       </c>
       <c r="O2" s="6">
-        <v>46289</v>
+        <v>46233</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="R2" s="5" t="s">
         <v>48</v>
@@ -4361,7 +4361,7 @@
         <v>49</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="U2" s="5" t="s">
         <v>49</v>
@@ -4373,7 +4373,7 @@
         <v>51</v>
       </c>
       <c r="Z2" s="7">
-        <v>976.64</v>
+        <v>1426.25</v>
       </c>
       <c r="AA2" s="7">
         <v>0</v>
@@ -4381,30 +4381,28 @@
       <c r="AB2" s="7">
         <v>0</v>
       </c>
-      <c r="AC2" s="6">
-        <v>46195</v>
-      </c>
+      <c r="AC2" s="6"/>
       <c r="AD2" s="7">
-        <v>976.64</v>
+        <v>1426.25</v>
       </c>
       <c r="AE2" s="4">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="AF2" s="5" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="AG2" s="5"/>
       <c r="AH2" s="5"/>
       <c r="AI2" s="5"/>
       <c r="AJ2" s="4"/>
       <c r="AK2" s="5" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="AL2" s="5" t="s">
         <v>54</v>
       </c>
       <c r="AM2" s="6">
-        <v>46182</v>
+        <v>46180</v>
       </c>
       <c r="AN2" s="5" t="s">
         <v>55</v>
@@ -4415,46 +4413,66 @@
         <v>530</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="C3" s="3"/>
+        <v>531</v>
+      </c>
+      <c r="C3" s="3">
+        <v>46195</v>
+      </c>
       <c r="D3" s="4">
-        <v>558642005</v>
+        <v>560450629</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>158</v>
+        <v>101</v>
       </c>
       <c r="F3" s="6">
-        <v>46150</v>
+        <v>46169</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>159</v>
+        <v>102</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>159</v>
+        <v>102</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="K3" s="3"/>
-      <c r="L3" s="4" t="str">
+      <c r="L3" s="12">
         <f ca="1">IF($O3="","",$O3-TODAY())</f>
-        <v/>
-      </c>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="5"/>
+        <v>-14</v>
+      </c>
+      <c r="M3" s="12">
+        <f ca="1">IF($C3="","",$C3+180-TODAY())</f>
+        <v>72</v>
+      </c>
+      <c r="N3" s="12">
+        <f ca="1">IF($C3="","",$C3+180-TODAY())</f>
+        <v>72</v>
+      </c>
+      <c r="O3" s="6">
+        <v>46289</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>103</v>
+      </c>
       <c r="Q3" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
+        <v>104</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="U3" s="5" t="s">
+        <v>49</v>
+      </c>
       <c r="V3" s="5"/>
       <c r="W3" s="5"/>
       <c r="X3" s="5"/>
@@ -4462,7 +4480,7 @@
         <v>51</v>
       </c>
       <c r="Z3" s="7">
-        <v>1029.98</v>
+        <v>976.64</v>
       </c>
       <c r="AA3" s="7">
         <v>0</v>
@@ -4470,28 +4488,30 @@
       <c r="AB3" s="7">
         <v>0</v>
       </c>
-      <c r="AC3" s="6"/>
+      <c r="AC3" s="6">
+        <v>46195</v>
+      </c>
       <c r="AD3" s="7">
-        <v>1029.98</v>
+        <v>976.64</v>
       </c>
       <c r="AE3" s="4">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AF3" s="5" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="AG3" s="5"/>
       <c r="AH3" s="5"/>
       <c r="AI3" s="5"/>
       <c r="AJ3" s="4"/>
       <c r="AK3" s="5" t="s">
-        <v>157</v>
+        <v>76</v>
       </c>
       <c r="AL3" s="5" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="AM3" s="6">
-        <v>46188</v>
+        <v>46182</v>
       </c>
       <c r="AN3" s="5" t="s">
         <v>55</v>
@@ -4506,13 +4526,13 @@
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="4">
-        <v>560692149</v>
+        <v>558642005</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="F4" s="6">
-        <v>46171</v>
+        <v>46150</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>159</v>
@@ -4562,7 +4582,7 @@
         <v>1029.98</v>
       </c>
       <c r="AE4" s="4">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="AF4" s="5" t="s">
         <v>80</v>
@@ -4572,13 +4592,13 @@
       <c r="AI4" s="5"/>
       <c r="AJ4" s="4"/>
       <c r="AK4" s="5" t="s">
-        <v>97</v>
+        <v>157</v>
       </c>
       <c r="AL4" s="5" t="s">
         <v>86</v>
       </c>
       <c r="AM4" s="6">
-        <v>46182</v>
+        <v>46188</v>
       </c>
       <c r="AN4" s="5" t="s">
         <v>55</v>
@@ -4586,69 +4606,49 @@
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>40</v>
+        <v>530</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>41</v>
+        <v>532</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="4">
-        <v>559331282</v>
+        <v>560692149</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>42</v>
+        <v>167</v>
       </c>
       <c r="F5" s="6">
-        <v>46156</v>
+        <v>46171</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>43</v>
+        <v>159</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>43</v>
+        <v>159</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="K5" s="3">
-        <v>46244</v>
-      </c>
-      <c r="L5" s="12">
+        <v>160</v>
+      </c>
+      <c r="K5" s="3"/>
+      <c r="L5" s="4" t="str">
         <f ca="1">IF($O5="","",$O5-TODAY())</f>
-        <v>-57</v>
-      </c>
-      <c r="M5" s="12" t="str">
-        <f ca="1">IF($C5="","",$C5+180-TODAY())</f>
         <v/>
       </c>
-      <c r="N5" s="12" t="str">
-        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
-        <v/>
-      </c>
-      <c r="O5" s="6">
-        <v>46246</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>46</v>
-      </c>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="5"/>
       <c r="Q5" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="R5" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="S5" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="T5" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="U5" s="5" t="s">
-        <v>49</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="5"/>
+      <c r="U5" s="5"/>
       <c r="V5" s="5"/>
       <c r="W5" s="5"/>
       <c r="X5" s="5"/>
@@ -4656,7 +4656,7 @@
         <v>51</v>
       </c>
       <c r="Z5" s="7">
-        <v>1372.91</v>
+        <v>1029.98</v>
       </c>
       <c r="AA5" s="7">
         <v>0</v>
@@ -4666,26 +4666,26 @@
       </c>
       <c r="AC5" s="6"/>
       <c r="AD5" s="7">
-        <v>1372.91</v>
+        <v>1029.98</v>
       </c>
       <c r="AE5" s="4">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="AF5" s="5" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="AG5" s="5"/>
       <c r="AH5" s="5"/>
       <c r="AI5" s="5"/>
       <c r="AJ5" s="4"/>
       <c r="AK5" s="5" t="s">
-        <v>53</v>
+        <v>97</v>
       </c>
       <c r="AL5" s="5" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="AM5" s="6">
-        <v>46180</v>
+        <v>46182</v>
       </c>
       <c r="AN5" s="5" t="s">
         <v>55</v>
@@ -4696,14 +4696,14 @@
         <v>40</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="4">
-        <v>559334288</v>
+        <v>559331282</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="F6" s="6">
         <v>46156</v>
@@ -4718,7 +4718,7 @@
         <v>44</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="K6" s="3">
         <v>46244</v>
@@ -4763,7 +4763,7 @@
         <v>51</v>
       </c>
       <c r="Z6" s="7">
-        <v>1426.25</v>
+        <v>1372.91</v>
       </c>
       <c r="AA6" s="7">
         <v>0</v>
@@ -4773,13 +4773,13 @@
       </c>
       <c r="AC6" s="6"/>
       <c r="AD6" s="7">
-        <v>1426.25</v>
+        <v>1372.91</v>
       </c>
       <c r="AE6" s="4">
         <v>86</v>
       </c>
       <c r="AF6" s="5" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="AG6" s="5"/>
       <c r="AH6" s="5"/>
@@ -4803,62 +4803,62 @@
         <v>40</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="4">
-        <v>558887755</v>
+        <v>559334288</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F7" s="6">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="K7" s="3">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="L7" s="12">
         <f ca="1">IF($O7="","",$O7-TODAY())</f>
-        <v>-55</v>
+        <v>-57</v>
       </c>
       <c r="M7" s="12" t="str">
-        <f ca="1">IF($C7="","",$C7+90-TODAY())</f>
+        <f ca="1">IF($C7="","",$C7+180-TODAY())</f>
         <v/>
       </c>
       <c r="N7" s="12" t="str">
-        <f ca="1">IF($C7="","",$C7+90-TODAY())</f>
+        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
         <v/>
       </c>
       <c r="O7" s="6">
-        <v>46248</v>
+        <v>46246</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="R7" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S7" s="5" t="s">
         <v>49</v>
       </c>
       <c r="T7" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="U7" s="5" t="s">
         <v>49</v>
@@ -4870,7 +4870,7 @@
         <v>51</v>
       </c>
       <c r="Z7" s="7">
-        <v>976.64</v>
+        <v>1426.25</v>
       </c>
       <c r="AA7" s="7">
         <v>0</v>
@@ -4880,10 +4880,10 @@
       </c>
       <c r="AC7" s="6"/>
       <c r="AD7" s="7">
-        <v>976.64</v>
+        <v>1426.25</v>
       </c>
       <c r="AE7" s="4">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="AF7" s="5" t="s">
         <v>59</v>
@@ -4893,10 +4893,10 @@
       <c r="AI7" s="5"/>
       <c r="AJ7" s="4"/>
       <c r="AK7" s="5" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="AL7" s="5" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="AM7" s="6">
         <v>46180</v>
@@ -4910,64 +4910,62 @@
         <v>40</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="3">
-        <v>46189</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="C8" s="3"/>
       <c r="D8" s="4">
-        <v>559931934</v>
+        <v>558887755</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="F8" s="6">
-        <v>46162</v>
+        <v>46153</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="K8" s="3">
         <v>46245</v>
       </c>
       <c r="L8" s="12">
         <f ca="1">IF($O8="","",$O8-TODAY())</f>
-        <v>-51</v>
-      </c>
-      <c r="M8" s="12">
-        <f ca="1">IF($C8="","",$C8+180-TODAY())</f>
+        <v>-55</v>
+      </c>
+      <c r="M8" s="12" t="str">
+        <f ca="1">IF($C8="","",$C8+90-TODAY())</f>
+        <v/>
+      </c>
+      <c r="N8" s="12" t="str">
+        <f ca="1">IF($C8="","",$C8+90-TODAY())</f>
+        <v/>
+      </c>
+      <c r="O8" s="6">
+        <v>46248</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q8" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N8" s="12">
-        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
-        <v>251</v>
-      </c>
-      <c r="O8" s="6">
-        <v>46252</v>
-      </c>
-      <c r="P8" s="5" t="s">
+      <c r="R8" s="5" t="s">
         <v>46</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="R8" s="5" t="s">
-        <v>48</v>
       </c>
       <c r="S8" s="5" t="s">
         <v>49</v>
       </c>
       <c r="T8" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="U8" s="5" t="s">
         <v>49</v>
@@ -4979,7 +4977,7 @@
         <v>51</v>
       </c>
       <c r="Z8" s="7">
-        <v>792.54</v>
+        <v>976.64</v>
       </c>
       <c r="AA8" s="7">
         <v>0</v>
@@ -4987,32 +4985,28 @@
       <c r="AB8" s="7">
         <v>0</v>
       </c>
-      <c r="AC8" s="6">
-        <v>46196</v>
-      </c>
+      <c r="AC8" s="6"/>
       <c r="AD8" s="7">
-        <v>792.54</v>
+        <v>976.64</v>
       </c>
       <c r="AE8" s="4">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AF8" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="AG8" s="5" t="s">
-        <v>75</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="AG8" s="5"/>
       <c r="AH8" s="5"/>
       <c r="AI8" s="5"/>
       <c r="AJ8" s="4"/>
       <c r="AK8" s="5" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="AL8" s="5" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="AM8" s="6">
-        <v>46182</v>
+        <v>46180</v>
       </c>
       <c r="AN8" s="5" t="s">
         <v>55</v>
@@ -5023,16 +5017,16 @@
         <v>40</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C9" s="3">
-        <v>46183</v>
+        <v>46189</v>
       </c>
       <c r="D9" s="4">
-        <v>560175340</v>
+        <v>559931934</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F9" s="6">
         <v>46162</v>
@@ -5044,10 +5038,10 @@
         <v>71</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="K9" s="3">
         <v>46245</v>
@@ -5058,11 +5052,11 @@
       </c>
       <c r="M9" s="12">
         <f ca="1">IF($C9="","",$C9+180-TODAY())</f>
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="N9" s="12">
         <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="O9" s="6">
         <v>46252</v>
@@ -5092,7 +5086,7 @@
         <v>51</v>
       </c>
       <c r="Z9" s="7">
-        <v>396.27</v>
+        <v>792.54</v>
       </c>
       <c r="AA9" s="7">
         <v>0</v>
@@ -5101,25 +5095,25 @@
         <v>0</v>
       </c>
       <c r="AC9" s="6">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="AD9" s="7">
-        <v>396.27</v>
+        <v>792.54</v>
       </c>
       <c r="AE9" s="4">
         <v>80</v>
       </c>
       <c r="AF9" s="5" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AG9" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AH9" s="5"/>
       <c r="AI9" s="5"/>
       <c r="AJ9" s="4"/>
       <c r="AK9" s="5" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AL9" s="5" t="s">
         <v>54</v>
@@ -5136,53 +5130,55 @@
         <v>40</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" s="3"/>
+        <v>77</v>
+      </c>
+      <c r="C10" s="3">
+        <v>46183</v>
+      </c>
       <c r="D10" s="4">
-        <v>560027331</v>
+        <v>560175340</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F10" s="6">
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="K10" s="3">
         <v>46245</v>
       </c>
       <c r="L10" s="12">
         <f ca="1">IF($O10="","",$O10-TODAY())</f>
-        <v>-49</v>
-      </c>
-      <c r="M10" s="12" t="str">
+        <v>-51</v>
+      </c>
+      <c r="M10" s="12">
         <f ca="1">IF($C10="","",$C10+180-TODAY())</f>
-        <v/>
-      </c>
-      <c r="N10" s="12" t="str">
+        <v>60</v>
+      </c>
+      <c r="N10" s="12">
         <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
-        <v/>
+        <v>245</v>
       </c>
       <c r="O10" s="6">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="P10" s="5" t="s">
         <v>46</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="R10" s="5" t="s">
         <v>48</v>
@@ -5203,7 +5199,7 @@
         <v>51</v>
       </c>
       <c r="Z10" s="7">
-        <v>1426.25</v>
+        <v>396.27</v>
       </c>
       <c r="AA10" s="7">
         <v>0</v>
@@ -5211,25 +5207,29 @@
       <c r="AB10" s="7">
         <v>0</v>
       </c>
-      <c r="AC10" s="6"/>
+      <c r="AC10" s="6">
+        <v>46195</v>
+      </c>
       <c r="AD10" s="7">
-        <v>1426.25</v>
+        <v>396.27</v>
       </c>
       <c r="AE10" s="4">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AF10" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG10" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="AG10" s="5" t="s">
+        <v>74</v>
+      </c>
       <c r="AH10" s="5"/>
       <c r="AI10" s="5"/>
       <c r="AJ10" s="4"/>
       <c r="AK10" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="AL10" s="5" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="AM10" s="6">
         <v>46182</v>
@@ -5240,34 +5240,32 @@
     </row>
     <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C11" s="3">
-        <v>46183</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="C11" s="3"/>
       <c r="D11" s="4">
-        <v>560178463</v>
+        <v>560027331</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F11" s="6">
         <v>46164</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="K11" s="3">
         <v>46245</v>
@@ -5276,13 +5274,13 @@
         <f ca="1">IF($O11="","",$O11-TODAY())</f>
         <v>-49</v>
       </c>
-      <c r="M11" s="12">
+      <c r="M11" s="12" t="str">
         <f ca="1">IF($C11="","",$C11+180-TODAY())</f>
-        <v>60</v>
-      </c>
-      <c r="N11" s="12">
+        <v/>
+      </c>
+      <c r="N11" s="12" t="str">
         <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
-        <v>245</v>
+        <v/>
       </c>
       <c r="O11" s="6">
         <v>46254</v>
@@ -5291,7 +5289,7 @@
         <v>46</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="R11" s="5" t="s">
         <v>48</v>
@@ -5312,7 +5310,7 @@
         <v>51</v>
       </c>
       <c r="Z11" s="7">
-        <v>1372.91</v>
+        <v>1426.25</v>
       </c>
       <c r="AA11" s="7">
         <v>0</v>
@@ -5320,32 +5318,28 @@
       <c r="AB11" s="7">
         <v>0</v>
       </c>
-      <c r="AC11" s="6">
-        <v>46189</v>
-      </c>
+      <c r="AC11" s="6"/>
       <c r="AD11" s="7">
-        <v>1372.91</v>
+        <v>1426.25</v>
       </c>
       <c r="AE11" s="4">
         <v>78</v>
       </c>
       <c r="AF11" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="AG11" s="5" t="s">
-        <v>75</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="AG11" s="5"/>
       <c r="AH11" s="5"/>
       <c r="AI11" s="5"/>
       <c r="AJ11" s="4"/>
       <c r="AK11" s="5" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="AL11" s="5" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="AM11" s="6">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="AN11" s="5" t="s">
         <v>55</v>
@@ -5356,28 +5350,28 @@
         <v>87</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C12" s="3">
-        <v>46191</v>
+        <v>46183</v>
       </c>
       <c r="D12" s="4">
-        <v>560664762</v>
+        <v>560178463</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F12" s="6">
-        <v>46171</v>
+        <v>46164</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>91</v>
@@ -5387,27 +5381,27 @@
       </c>
       <c r="L12" s="12">
         <f ca="1">IF($O12="","",$O12-TODAY())</f>
-        <v>-42</v>
+        <v>-49</v>
       </c>
       <c r="M12" s="12">
-        <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
-        <v>253</v>
+        <f ca="1">IF($C12="","",$C12+180-TODAY())</f>
+        <v>60</v>
       </c>
       <c r="N12" s="12">
         <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="O12" s="6">
-        <v>46261</v>
+        <v>46254</v>
       </c>
       <c r="P12" s="5" t="s">
         <v>46</v>
       </c>
       <c r="Q12" s="5" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="R12" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S12" s="5" t="s">
         <v>49</v>
@@ -5434,29 +5428,31 @@
         <v>0</v>
       </c>
       <c r="AC12" s="6">
-        <v>46191</v>
+        <v>46189</v>
       </c>
       <c r="AD12" s="7">
         <v>1372.91</v>
       </c>
       <c r="AE12" s="4">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="AF12" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG12" s="5"/>
+        <v>92</v>
+      </c>
+      <c r="AG12" s="5" t="s">
+        <v>75</v>
+      </c>
       <c r="AH12" s="5"/>
       <c r="AI12" s="5"/>
       <c r="AJ12" s="4"/>
       <c r="AK12" s="5" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="AL12" s="5" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="AM12" s="6">
-        <v>46182</v>
+        <v>46181</v>
       </c>
       <c r="AN12" s="5" t="s">
         <v>55</v>
@@ -5464,59 +5460,61 @@
     </row>
     <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="C13" s="3"/>
+        <v>93</v>
+      </c>
+      <c r="C13" s="3">
+        <v>46191</v>
+      </c>
       <c r="D13" s="4">
-        <v>558010066</v>
+        <v>560664762</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F13" s="6">
-        <v>46143</v>
+        <v>46171</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="K13" s="3">
-        <v>46300</v>
+        <v>46245</v>
       </c>
       <c r="L13" s="12">
         <f ca="1">IF($O13="","",$O13-TODAY())</f>
-        <v>-70</v>
-      </c>
-      <c r="M13" s="12" t="str">
-        <f ca="1">IF($C13="","",$C13+180-TODAY())</f>
-        <v/>
-      </c>
-      <c r="N13" s="12" t="str">
+        <v>-42</v>
+      </c>
+      <c r="M13" s="12">
         <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
-        <v/>
+        <v>253</v>
+      </c>
+      <c r="N13" s="12">
+        <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
+        <v>253</v>
       </c>
       <c r="O13" s="6">
-        <v>46233</v>
+        <v>46261</v>
       </c>
       <c r="P13" s="5" t="s">
         <v>46</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="R13" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S13" s="5" t="s">
         <v>49</v>
@@ -5534,7 +5532,7 @@
         <v>51</v>
       </c>
       <c r="Z13" s="7">
-        <v>1426.25</v>
+        <v>1372.91</v>
       </c>
       <c r="AA13" s="7">
         <v>0</v>
@@ -5542,12 +5540,14 @@
       <c r="AB13" s="7">
         <v>0</v>
       </c>
-      <c r="AC13" s="6"/>
+      <c r="AC13" s="6">
+        <v>46191</v>
+      </c>
       <c r="AD13" s="7">
-        <v>1426.25</v>
+        <v>1372.91</v>
       </c>
       <c r="AE13" s="4">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="AF13" s="5" t="s">
         <v>80</v>
@@ -5557,13 +5557,13 @@
       <c r="AI13" s="5"/>
       <c r="AJ13" s="4"/>
       <c r="AK13" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="AL13" s="5" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="AM13" s="6">
-        <v>46180</v>
+        <v>46182</v>
       </c>
       <c r="AN13" s="5" t="s">
         <v>55</v>
@@ -17430,7 +17430,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>541</v>
       </c>

--- a/SPC26S1 - 05 May.xlsx
+++ b/SPC26S1 - 05 May.xlsx
@@ -2654,7 +2654,7 @@
     <t xml:space="preserve">    5 - No limit on file: 11</t>
   </si>
   <si>
-    <t>'ALL Claims 2026-S1 - Master.xlsx' (same folder) holds all 482 claims for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
+    <t>'ALL Claims 2026-S1 - Master.xlsx' (same folder) holds all 477 claims for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
   </si>
   <si>
     <t>Resubmitted again - Aisha review Adlers status on the AHCCCS portal. He is showing active ins 2012 - Rendering OON with Medicaid AHCCCS - Confirming with Bri - DOS we were working on 05/01/2026</t>
